--- a/CostBreakdown.xlsx
+++ b/CostBreakdown.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ceaa8977d2236823/Documents/GitHub/451-DBF-Team01/Cost Breakdown/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jpreisle\Documents\GitHub\451-DBF-Team01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="8_{06C48DBD-8120-4A61-B94D-149F3D8EF4DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02B58D71-5131-419B-8AE6-DBD08CD8EA5B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C604338-92F2-42DA-A9D2-C3D9184980AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C684E4FE-65D8-41BB-8319-3046AEA9131B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="831" activeTab="3" xr2:uid="{C684E4FE-65D8-41BB-8319-3046AEA9131B}"/>
   </bookViews>
   <sheets>
     <sheet name="Aircraft Cost Grand Total" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Avionics BOM" sheetId="2" r:id="rId3"/>
     <sheet name="Structures BOM" sheetId="3" r:id="rId4"/>
     <sheet name="Mechanisms BOM" sheetId="4" r:id="rId5"/>
-    <sheet name="Miscellaneous BOM" sheetId="5" r:id="rId6"/>
+    <sheet name="Propulsion BOM" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,9 +43,254 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="79">
+  <si>
+    <t>GPS Tray</t>
+  </si>
+  <si>
+    <t>Reciever Tray</t>
+  </si>
+  <si>
+    <t>M4 30mm bolt</t>
+  </si>
+  <si>
+    <t>M4 60mm bolt</t>
+  </si>
+  <si>
+    <t>Part</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Total Cost</t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>10x7E Prop</t>
+  </si>
+  <si>
+    <t>Cobra 3520/10</t>
+  </si>
+  <si>
+    <t>RC Electric Parts 80A ESC</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Airspeed Sensor Extension Wire</t>
+  </si>
+  <si>
+    <t>M4 x 0.7mm washer</t>
+  </si>
+  <si>
+    <t>M4 think locknut</t>
+  </si>
+  <si>
+    <t>Turnigy 4Cell 4000 mAh Battery</t>
+  </si>
+  <si>
+    <t>2ft x 1.125 x 1.125 in extruded L Aluminum</t>
+  </si>
+  <si>
+    <t>1/16 x 1/2 x 1/2 aluminum tube - 6ft</t>
+  </si>
+  <si>
+    <t>Plywood 4x8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foam Board </t>
+  </si>
+  <si>
+    <t>Servo Mount</t>
+  </si>
+  <si>
+    <t>Control Horns</t>
+  </si>
+  <si>
+    <t>Aluminum Wire</t>
+  </si>
+  <si>
+    <t>Super Glue</t>
+  </si>
+  <si>
+    <t>Main Landing Gear</t>
+  </si>
+  <si>
+    <t>Rear Landing Gear</t>
+  </si>
+  <si>
+    <t>Main Landing Gear Wheels</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/products/6546k49/</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/products/8982k6/</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/products/93475a230/</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/products/90453a112/</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/products/91290a172/</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/products/91290a647/</t>
+  </si>
+  <si>
+    <t>https://www.homedepot.com/p/Plytanium-1-4-in-x-4-ft-x-8-ft-BC-Sanded-Pine-Plywood-235552/100063669</t>
+  </si>
+  <si>
+    <t>https://www.homedepot.com/p/Owens-Corning-FOAMULAR-NGX-F-250-2-in-x-4-ft-x-8-ft-SSE-R-10-XPS-Rigid-Foam-Board-Insulation-52DDNGX/315197962</t>
+  </si>
+  <si>
+    <t>https://www.apcprop.com/product/10x7e/?v=0b3b97fa6688</t>
+  </si>
+  <si>
+    <t>Purchased</t>
+  </si>
+  <si>
+    <t>Assembly</t>
+  </si>
+  <si>
+    <t>Avionics</t>
+  </si>
+  <si>
+    <t>Structures</t>
+  </si>
+  <si>
+    <t>Mechanism</t>
+  </si>
+  <si>
+    <t>Propulsion</t>
+  </si>
+  <si>
+    <t>https://www.cobramotorsusa.com/motors-3520-10.html</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/RC-Electric-Controller-Brushless-Motors/dp/B071GRSFBD?th=1</t>
+  </si>
+  <si>
+    <t>https://hobbyking.com/en_us/turnigy-battery-4000mah-4s-30c-lipo-pack-xt-60.html?srsltid=AU7gw4WVGopDsORjxCL-xylPi1hT8fcP1h7w3tHevpSY-TgKOw5vp4lY</t>
+  </si>
+  <si>
+    <t>Wood Glue</t>
+  </si>
+  <si>
+    <t>Battery Strap</t>
+  </si>
+  <si>
+    <t>Zip Ties</t>
+  </si>
+  <si>
+    <t>mg90s servo</t>
+  </si>
+  <si>
+    <t>Printed</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/Miuzei-Geared-Helicopter-Arduino-Project/dp/B0CP98TZJ2/ref=sr_1_1_sspa?crid=3UWKW3AUXSAKT&amp;dib=eyJ2IjoiMSJ9.EdycfDxnDtcyy4IWKKo05CT4vxdxksMXHI4KVwvilewG4LFzZMiLD-SKTNAvfkn4n3bvzzknFtE5jqLS00GcsR7QSNBrrplhBsFkdc5C7iyFYKU1_Vb1mhk3C7o5-PxM_34Q6HMkAV_urpdOH6vLjHjf_mxsGFtruVyux7qyyMBxdQ_rSkVFyQGAwCDKCI88NTD0eIyd3TvFcExUWLg1DTeMO4Dq4BhMZDTM3cre_Y5T8fpD7C6svcrSYhyshFkTslJFxTQ2ECM_4oD4NXBrL1JYotARBhRZd5SXqmh1hWg.VKHwGgs_7fH_kPtCF2In0AiV3-5WYmgh5fjs7UV6F28&amp;dib_tag=se&amp;keywords=mg90s%2Bservo&amp;qid=1791318944&amp;s=toys-and-games&amp;sprefix=mg90s%2Bservo%2Ctoys-and-games%2C163&amp;sr=1-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1</t>
+  </si>
+  <si>
+    <t>Packing Tape</t>
+  </si>
+  <si>
+    <t>https://www.homedepot.com/p/Scotch-1-88-in-x-54-6-yds-Heavy-Duty-Clear-Shipping-and-Packaging-Tape-3850-DC/304884808</t>
+  </si>
+  <si>
+    <t>https://www.homedepot.com/p/Loctite-Super-Glue-0-14-oz-Ultra-Gel-Control-Clear-Applicator-1363589/202020461</t>
+  </si>
+  <si>
+    <t>Airspeed Sensor Print</t>
+  </si>
+  <si>
+    <t>Tail Mount Print</t>
+  </si>
+  <si>
+    <t>Wing Dihedral Print</t>
+  </si>
+  <si>
+    <t>https://www.homedepot.com/pep/E6000-2-oz-Clear-Adhesive-800432/333376257?g_store=2034&amp;source=shoppingads&amp;locale=en-US&amp;fp=ggl&amp;pla&amp;mtc=SHOPPING-BF-CDP-GGL-D24-024_004_ADHESIVES-NA-NA-NA-PMAX-NA-NA-NA-NA-NBR-NA-NA-NEW-NA_FY25&amp;cm_mmc=SHOPPING-BF-CDP-GGL-D24-024_004_ADHESIVES-NA-NA-NA-PMAX-NA-NA-NA-NA-NBR-NA-NA-NEW-NA_FY25-22204253200--&amp;gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=22204272157&amp;gbraid=0AAAAADq61UcsMashMLoaXkRspH99Y273H&amp;gclid=Cj0KCQjwuJLWBhD_ARIsAIBcRUwCF8rR0SLtACCiYZZMOikqfTXq54H3iKsptby3r_ci7TjzcJ3QqQUaAkesEALw_wcB</t>
+  </si>
+  <si>
+    <t>1/16 x 1/2 x 1/2 aluminum tube - 3ft</t>
+  </si>
+  <si>
+    <t>Aluminum Tube 6 in (Spacer</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/products/8978k911/</t>
+  </si>
+  <si>
+    <t>made from aluminum l bracket</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/products/91274a122/</t>
+  </si>
+  <si>
+    <t>M4 25mm bolt</t>
+  </si>
+  <si>
+    <t>https://www.horizonhobby.com/product/wheel-set-3-carbon-z-t-28/EFL1310.html</t>
+  </si>
+  <si>
+    <t>https://www.horizonhobby.com/product/landing-gear-pawnee-brave-20cc/HAN703509.html</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/Wheel-Assembly-60x25mm-Airplane-Replacement/dp/B019IF9PYE/ref=sr_1_3?crid=1KQYSK0JD4ZZH&amp;dib=eyJ2IjoiMSJ9.8MRt66ofaD-HTPbzJODgG9Qlz2FdPJ91tUSbi09ZX4lr_dHuf2NKoZS7yXkhGvsVO7_WKa_ohMkEsAFLxwt-2Y5LjVyLB1w62LlVb4eYR7M8uBNnncHVAWHKkTz9-JcB18VPXtECOdf-9qaDpfuOhcmxJ7khZT4ibu6UjMTIr81ZbuFd9GNoDpglMVs6y9SRzNO55tNk5TOhnozD2gA5eQOHEgP1Wff9-jEDt36BmgqJ2T0Mya91gIEOvEKWIuxuJ8YbR1seAbvyWi-_NiKZqcaMePTvVA3bQu5wYEkgSmw.9Q_KCk60K2yh_idKVDyKAwH8DcX-mFqYibwQmQG3fHg&amp;dib_tag=se&amp;keywords=hobbypark+tailwheel+assembly&amp;qid=1790866317&amp;sprefix=hobbypark+tailwheel+assembl%2Caps%2C146&amp;sr=8-3</t>
+  </si>
+  <si>
+    <t>Used Bambu Fillament Prices</t>
+  </si>
+  <si>
+    <t>Motor Cover Print</t>
+  </si>
+  <si>
+    <t>Doorhinge</t>
+  </si>
+  <si>
+    <t>Servo Extension Wires 36 in</t>
+  </si>
+  <si>
+    <t>https://www.readymaderc.com/products/details/90cm-36in-jr-22awg-servo-cable?gad_source=1&amp;gad_campaignid=17190799136&amp;gbraid=0AAAAADpShvX0lNZ7R-rR4kFhQhZqXsQe4&amp;gclid=Cj0KCQjwuJLWBhD_ARIsAIBcRUwmkykbpZ-Yv1Mmf8ESymVjGKAtao29dLx49Bg4_qsVj1gg-xdR5fkaAsFtEALw_wcB#technical-info-tab</t>
+  </si>
+  <si>
+    <t>Servo extension wire 24 in</t>
+  </si>
+  <si>
+    <t>ESC holddown</t>
+  </si>
+  <si>
+    <t>https://www.readymaderc.com/products/details/60cm-24-inch-jr-style-22awg-twisted-servo-cable</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/16175A561/</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/2113N16/</t>
+  </si>
+  <si>
+    <t>https://www.readymaderc.com/products/details/strix-battery-strap-20-300-mm-2pcs</t>
+  </si>
+  <si>
+    <t>Rubber Bands</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -53,13 +298,35 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -71,16 +338,63 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -413,10 +727,33 @@
   <sheetPr>
     <tabColor theme="5"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="4">
+        <f>SUM('Per Assembly Cost --&gt;'!B:B)</f>
+        <v>404.95</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B1">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+      <formula>400</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
+      <formula>400</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -425,9 +762,58 @@
   <sheetPr>
     <tabColor theme="1"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.28515625" customWidth="1"/>
+    <col min="2" max="2" width="22.85546875" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="1">
+        <f>SUM('Avionics BOM'!D:D)</f>
+        <v>18.320000000000004</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="1">
+        <f>SUM('Structures BOM'!D:D)</f>
+        <v>183.05999999999997</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="1">
+        <f>SUM('Mechanisms BOM'!D:D)</f>
+        <v>62.879999999999995</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="1">
+        <f>SUM('Propulsion BOM'!D:D)</f>
+        <v>140.69</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -437,9 +823,188 @@
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30.28515625" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="1"/>
+    <col min="4" max="4" width="10.28515625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="1">
+        <v>4</v>
+      </c>
+      <c r="D2" s="1">
+        <v>7.16</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1.59</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="1">
+        <v>100</v>
+      </c>
+      <c r="D8" s="5">
+        <v>7.42</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="1">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0.52</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" s="1">
+        <v>1</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" location="technical-info-tab" display="https://www.readymaderc.com/products/details/90cm-36in-jr-22awg-servo-cable?gad_source=1&amp;gad_campaignid=17190799136&amp;gbraid=0AAAAADpShvX0lNZ7R-rR4kFhQhZqXsQe4&amp;gclid=Cj0KCQjwuJLWBhD_ARIsAIBcRUwmkykbpZ-Yv1Mmf8ESymVjGKAtao29dLx49Bg4_qsVj1gg-xdR5fkaAsFtEALw_wcB#technical-info-tab" xr:uid="{7C16D964-E42A-476D-8667-EA7484666847}"/>
+    <hyperlink ref="E3" r:id="rId2" xr:uid="{AA186CBF-1F4D-4354-8F4C-254D5CF88C30}"/>
+    <hyperlink ref="E8" r:id="rId3" xr:uid="{1CEF71FE-8065-4760-8150-4B4B1DA37CD5}"/>
+    <hyperlink ref="E7" r:id="rId4" xr:uid="{4EAF33CA-E17C-43DA-8633-E519A1EDF818}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -449,9 +1014,339 @@
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="37.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="1"/>
+    <col min="5" max="5" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1">
+        <v>26.26</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5">
+        <v>55.6</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="1">
+        <v>5</v>
+      </c>
+      <c r="D4" s="6">
+        <v>2.97</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="1">
+        <v>25</v>
+      </c>
+      <c r="D5" s="1">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="1">
+        <v>25</v>
+      </c>
+      <c r="D6" s="1">
+        <v>5.55</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="1">
+        <v>100</v>
+      </c>
+      <c r="D7" s="1">
+        <v>3.93</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="1">
+        <v>25</v>
+      </c>
+      <c r="D8" s="1">
+        <v>7.14</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="1">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1">
+        <v>24.6</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="1">
+        <v>1</v>
+      </c>
+      <c r="D10" s="1">
+        <v>14.27</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="1">
+        <v>1</v>
+      </c>
+      <c r="D11" s="1">
+        <v>6.89</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1">
+        <v>5.98</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="1">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1">
+        <f>4.48*3</f>
+        <v>13.440000000000001</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="1">
+        <v>1</v>
+      </c>
+      <c r="D14" s="6">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>51</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="1">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5">
+        <v>5.98</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1</v>
+      </c>
+      <c r="D16" s="1">
+        <v>0.06</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="1">
+        <v>1</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="1">
+        <v>1</v>
+      </c>
+      <c r="D18" s="1">
+        <v>0.96</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E11" r:id="rId1" xr:uid="{9B3802E2-0DAA-4495-8E7B-C8A9F6A2FFA8}"/>
+    <hyperlink ref="E9" r:id="rId2" xr:uid="{751BAEB2-26DC-4CAF-8D96-A38FD9446E87}"/>
+    <hyperlink ref="E7" r:id="rId3" xr:uid="{3C1E28BD-D3E4-46AC-A0D8-E327EE566BE4}"/>
+    <hyperlink ref="E8" r:id="rId4" xr:uid="{77BD64C6-BF95-404A-B01F-81F95BAFFFCD}"/>
+    <hyperlink ref="E4" r:id="rId5" xr:uid="{675196D7-5C58-487C-8B15-98E28F3CC124}"/>
+    <hyperlink ref="E6" r:id="rId6" xr:uid="{DAE67438-2EA2-46E6-AE59-3CE1BA52DE6A}"/>
+    <hyperlink ref="E2" r:id="rId7" xr:uid="{20180B92-8ABC-43AC-BBB8-7C093E6B2F3E}"/>
+    <hyperlink ref="E3" r:id="rId8" xr:uid="{EE40E960-AE93-490E-8684-32B42CB94C63}"/>
+    <hyperlink ref="E15" r:id="rId9" xr:uid="{6293C65C-7FE4-4A84-B068-EDC9724F2BCC}"/>
+    <hyperlink ref="E12" r:id="rId10" xr:uid="{4107E890-CEA7-4F2F-B7A9-E682D7C164AD}"/>
+    <hyperlink ref="E14" r:id="rId11" xr:uid="{A91A1DE5-4331-40CB-B90C-715E0BCCB855}"/>
+    <hyperlink ref="E10" r:id="rId12" xr:uid="{A329B7F4-245D-42E5-AACE-0CD364DDF33B}"/>
+    <hyperlink ref="E5" r:id="rId13" xr:uid="{410C3B3D-E226-4918-926D-2343FE7E95FB}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -461,9 +1356,185 @@
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="1"/>
+    <col min="4" max="4" width="10.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="1">
+        <v>4</v>
+      </c>
+      <c r="D2" s="1">
+        <v>13.88</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="1">
+        <v>4</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="1">
+        <v>4</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5">
+        <v>16.989999999999998</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="1">
+        <v>3</v>
+      </c>
+      <c r="D7" s="5">
+        <v>16.989999999999998</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="1">
+        <v>1</v>
+      </c>
+      <c r="D8" s="1">
+        <v>8.9700000000000006</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="1">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1">
+        <v>5.52</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="1">
+        <v>8</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="E10" s="8"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E7" r:id="rId1" xr:uid="{53C4CC5E-18BB-493C-B4BF-A5DBA279DD54}"/>
+    <hyperlink ref="E6" r:id="rId2" xr:uid="{0004C175-5738-4B8F-BD83-32A5A30FB28E}"/>
+    <hyperlink ref="E9" r:id="rId3" xr:uid="{8D7210AE-DB3A-46B9-AA95-7FD3E6229A86}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -473,31 +1544,113 @@
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="28" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1">
+        <v>3.64</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1">
+        <v>57.99</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1">
+        <v>38.49</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1">
+        <v>40.57</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{F52A4918-E897-4C4E-897E-D5215E045CA6}"/>
+    <hyperlink ref="E3" r:id="rId2" xr:uid="{33A92E14-CC68-4656-B82C-8BE565F4FCFD}"/>
+    <hyperlink ref="E4" r:id="rId3" xr:uid="{50C17E5A-DE64-49D2-A6A1-C7139C62E0DA}"/>
+    <hyperlink ref="E5" r:id="rId4" xr:uid="{B212F068-A19C-47FA-90E5-D3A0FCB21397}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c440327c-db0c-40f7-973b-7bc2ae283ce2" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006F9431A864773547893222757859AEDB" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8d93b3794edbd64c1f12ce1859fb2ebb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c440327c-db0c-40f7-973b-7bc2ae283ce2" xmlns:ns4="3bf09d50-f695-4e18-a2ec-955b0ff6d5dc" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ab198344f7607dd971ab6c53863418c3" ns3:_="" ns4:_="">
     <xsd:import namespace="c440327c-db0c-40f7-973b-7bc2ae283ce2"/>
@@ -722,32 +1875,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F120B44-02FC-4D2A-B0A5-AADC531A6E78}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="c440327c-db0c-40f7-973b-7bc2ae283ce2"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="3bf09d50-f695-4e18-a2ec-955b0ff6d5dc"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{140E0E22-42B5-4B4A-934D-04548B25B00B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c440327c-db0c-40f7-973b-7bc2ae283ce2" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92C5615A-B0FE-40B8-955A-C3851BD0A604}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -764,4 +1909,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{140E0E22-42B5-4B4A-934D-04548B25B00B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F120B44-02FC-4D2A-B0A5-AADC531A6E78}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="c440327c-db0c-40f7-973b-7bc2ae283ce2"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="3bf09d50-f695-4e18-a2ec-955b0ff6d5dc"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/CostBreakdown.xlsx
+++ b/CostBreakdown.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jpreisle\Documents\GitHub\451-DBF-Team01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C604338-92F2-42DA-A9D2-C3D9184980AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A15732B-2493-4347-80F7-F7BEBAB7EC46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="831" activeTab="3" xr2:uid="{C684E4FE-65D8-41BB-8319-3046AEA9131B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="831" activeTab="5" xr2:uid="{C684E4FE-65D8-41BB-8319-3046AEA9131B}"/>
   </bookViews>
   <sheets>
     <sheet name="Aircraft Cost Grand Total" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="80">
   <si>
     <t>GPS Tray</t>
   </si>
@@ -281,6 +281,9 @@
   </si>
   <si>
     <t>Rubber Bands</t>
+  </si>
+  <si>
+    <t>Cube Holddown Print</t>
   </si>
 </sst>
 </file>
@@ -342,7 +345,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -357,9 +360,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -740,7 +740,7 @@
       </c>
       <c r="B1" s="4">
         <f>SUM('Per Assembly Cost --&gt;'!B:B)</f>
-        <v>404.95</v>
+        <v>405.05</v>
       </c>
     </row>
   </sheetData>
@@ -783,7 +783,7 @@
       </c>
       <c r="B2" s="1">
         <f>SUM('Avionics BOM'!D:D)</f>
-        <v>18.320000000000004</v>
+        <v>18.420000000000005</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -823,7 +823,7 @@
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.28515625" customWidth="1"/>
@@ -995,6 +995,23 @@
         <v>0.1</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>79</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>67</v>
       </c>
     </row>
@@ -1051,7 +1068,7 @@
       <c r="C2" s="1">
         <v>1</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="5">
         <v>26.26</v>
       </c>
       <c r="E2" s="3" t="s">
@@ -1085,7 +1102,7 @@
       <c r="C4" s="1">
         <v>5</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="1">
         <v>2.97</v>
       </c>
       <c r="E4" s="3" t="s">
@@ -1238,7 +1255,7 @@
       <c r="C13" s="1">
         <v>3</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D13" s="5">
         <f>4.48*3</f>
         <v>13.440000000000001</v>
       </c>
@@ -1256,7 +1273,7 @@
       <c r="C14" s="1">
         <v>1</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="1">
         <v>4.2300000000000004</v>
       </c>
       <c r="E14" s="3" t="s">
@@ -1291,7 +1308,7 @@
         <v>1</v>
       </c>
       <c r="D16" s="1">
-        <v>0.06</v>
+        <v>0.6</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>67</v>
@@ -1308,7 +1325,7 @@
         <v>1</v>
       </c>
       <c r="D17" s="1">
-        <v>0.6</v>
+        <v>0.06</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>67</v>
@@ -1430,7 +1447,7 @@
       <c r="D4" s="1">
         <v>0</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1527,7 +1544,7 @@
       <c r="D10" s="1">
         <v>0.2</v>
       </c>
-      <c r="E10" s="8"/>
+      <c r="E10" s="7"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1651,6 +1668,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c440327c-db0c-40f7-973b-7bc2ae283ce2" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006F9431A864773547893222757859AEDB" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8d93b3794edbd64c1f12ce1859fb2ebb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c440327c-db0c-40f7-973b-7bc2ae283ce2" xmlns:ns4="3bf09d50-f695-4e18-a2ec-955b0ff6d5dc" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ab198344f7607dd971ab6c53863418c3" ns3:_="" ns4:_="">
     <xsd:import namespace="c440327c-db0c-40f7-973b-7bc2ae283ce2"/>
@@ -1875,24 +1909,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F120B44-02FC-4D2A-B0A5-AADC531A6E78}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="c440327c-db0c-40f7-973b-7bc2ae283ce2"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="3bf09d50-f695-4e18-a2ec-955b0ff6d5dc"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c440327c-db0c-40f7-973b-7bc2ae283ce2" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{140E0E22-42B5-4B4A-934D-04548B25B00B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92C5615A-B0FE-40B8-955A-C3851BD0A604}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1909,29 +1951,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{140E0E22-42B5-4B4A-934D-04548B25B00B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F120B44-02FC-4D2A-B0A5-AADC531A6E78}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="c440327c-db0c-40f7-973b-7bc2ae283ce2"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="3bf09d50-f695-4e18-a2ec-955b0ff6d5dc"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/CostBreakdown.xlsx
+++ b/CostBreakdown.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jpreisle\Documents\GitHub\451-DBF-Team01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A15732B-2493-4347-80F7-F7BEBAB7EC46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D52E995-D2A9-4830-A836-EB88AB3C16BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="831" activeTab="5" xr2:uid="{C684E4FE-65D8-41BB-8319-3046AEA9131B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="831" activeTab="2" xr2:uid="{C684E4FE-65D8-41BB-8319-3046AEA9131B}"/>
   </bookViews>
   <sheets>
     <sheet name="Aircraft Cost Grand Total" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="81">
   <si>
     <t>GPS Tray</t>
   </si>
@@ -284,6 +284,9 @@
   </si>
   <si>
     <t>Cube Holddown Print</t>
+  </si>
+  <si>
+    <t>MAY NEED TO REPLACE WITH TUBING AND PUT AIRSPEED SENSOR IN FUSELAGE</t>
   </si>
 </sst>
 </file>
@@ -929,6 +932,9 @@
         <v>1</v>
       </c>
       <c r="D6" s="5"/>
+      <c r="E6" s="6" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -1676,15 +1682,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006F9431A864773547893222757859AEDB" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8d93b3794edbd64c1f12ce1859fb2ebb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c440327c-db0c-40f7-973b-7bc2ae283ce2" xmlns:ns4="3bf09d50-f695-4e18-a2ec-955b0ff6d5dc" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ab198344f7607dd971ab6c53863418c3" ns3:_="" ns4:_="">
     <xsd:import namespace="c440327c-db0c-40f7-973b-7bc2ae283ce2"/>
@@ -1909,6 +1906,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F120B44-02FC-4D2A-B0A5-AADC531A6E78}">
   <ds:schemaRefs>
@@ -1927,14 +1933,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{140E0E22-42B5-4B4A-934D-04548B25B00B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92C5615A-B0FE-40B8-955A-C3851BD0A604}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1951,4 +1949,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{140E0E22-42B5-4B4A-934D-04548B25B00B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/CostBreakdown.xlsx
+++ b/CostBreakdown.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jpreisle\Documents\GitHub\451-DBF-Team01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D52E995-D2A9-4830-A836-EB88AB3C16BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E44A072-D54E-4D41-AA72-4500457D5945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="831" activeTab="2" xr2:uid="{C684E4FE-65D8-41BB-8319-3046AEA9131B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="831" activeTab="3" xr2:uid="{C684E4FE-65D8-41BB-8319-3046AEA9131B}"/>
   </bookViews>
   <sheets>
     <sheet name="Aircraft Cost Grand Total" sheetId="1" r:id="rId1"/>
@@ -229,9 +229,6 @@
     <t>https://www.mcmaster.com/products/8978k911/</t>
   </si>
   <si>
-    <t>made from aluminum l bracket</t>
-  </si>
-  <si>
     <t>https://www.mcmaster.com/products/91274a122/</t>
   </si>
   <si>
@@ -287,6 +284,9 @@
   </si>
   <si>
     <t>MAY NEED TO REPLACE WITH TUBING AND PUT AIRSPEED SENSOR IN FUSELAGE</t>
+  </si>
+  <si>
+    <t>made from aluminum l=L bracket</t>
   </si>
 </sst>
 </file>
@@ -855,7 +855,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>36</v>
@@ -867,12 +867,12 @@
         <v>7.16</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>36</v>
@@ -884,7 +884,7 @@
         <v>1.59</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -901,7 +901,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -918,7 +918,7 @@
         <v>0.4</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -933,7 +933,7 @@
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -950,7 +950,7 @@
         <v>0.99</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -967,7 +967,7 @@
         <v>7.42</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -984,12 +984,12 @@
         <v>0.52</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>49</v>
@@ -1001,12 +1001,12 @@
         <v>0.1</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>49</v>
@@ -1018,7 +1018,7 @@
         <v>0.1</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1117,7 +1117,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>36</v>
@@ -1129,7 +1129,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -1317,7 +1317,7 @@
         <v>0.6</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -1334,12 +1334,12 @@
         <v>0.06</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>49</v>
@@ -1351,7 +1351,7 @@
         <v>0.96</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1437,7 +1437,7 @@
         <v>0.33</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -1454,7 +1454,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -1483,7 +1483,7 @@
         <v>16.989999999999998</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -1500,7 +1500,7 @@
         <v>16.989999999999998</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -1517,12 +1517,12 @@
         <v>8.9700000000000006</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>36</v>
@@ -1534,12 +1534,12 @@
         <v>5.52</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>36</v>
@@ -1674,11 +1674,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c440327c-db0c-40f7-973b-7bc2ae283ce2" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1907,27 +1908,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c440327c-db0c-40f7-973b-7bc2ae283ce2" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F120B44-02FC-4D2A-B0A5-AADC531A6E78}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{140E0E22-42B5-4B4A-934D-04548B25B00B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="c440327c-db0c-40f7-973b-7bc2ae283ce2"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="3bf09d50-f695-4e18-a2ec-955b0ff6d5dc"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1952,9 +1943,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{140E0E22-42B5-4B4A-934D-04548B25B00B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F120B44-02FC-4D2A-B0A5-AADC531A6E78}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="c440327c-db0c-40f7-973b-7bc2ae283ce2"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="3bf09d50-f695-4e18-a2ec-955b0ff6d5dc"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/CostBreakdown.xlsx
+++ b/CostBreakdown.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jpreisle\Documents\GitHub\451-DBF-Team01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E44A072-D54E-4D41-AA72-4500457D5945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0DE1F80-DDED-4D6C-B75C-BCA8321A3CE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="831" activeTab="3" xr2:uid="{C684E4FE-65D8-41BB-8319-3046AEA9131B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="831" activeTab="5" xr2:uid="{C684E4FE-65D8-41BB-8319-3046AEA9131B}"/>
   </bookViews>
   <sheets>
     <sheet name="Aircraft Cost Grand Total" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="82">
   <si>
     <t>GPS Tray</t>
   </si>
@@ -199,12 +199,6 @@
     <t>https://www.amazon.com/Miuzei-Geared-Helicopter-Arduino-Project/dp/B0CP98TZJ2/ref=sr_1_1_sspa?crid=3UWKW3AUXSAKT&amp;dib=eyJ2IjoiMSJ9.EdycfDxnDtcyy4IWKKo05CT4vxdxksMXHI4KVwvilewG4LFzZMiLD-SKTNAvfkn4n3bvzzknFtE5jqLS00GcsR7QSNBrrplhBsFkdc5C7iyFYKU1_Vb1mhk3C7o5-PxM_34Q6HMkAV_urpdOH6vLjHjf_mxsGFtruVyux7qyyMBxdQ_rSkVFyQGAwCDKCI88NTD0eIyd3TvFcExUWLg1DTeMO4Dq4BhMZDTM3cre_Y5T8fpD7C6svcrSYhyshFkTslJFxTQ2ECM_4oD4NXBrL1JYotARBhRZd5SXqmh1hWg.VKHwGgs_7fH_kPtCF2In0AiV3-5WYmgh5fjs7UV6F28&amp;dib_tag=se&amp;keywords=mg90s%2Bservo&amp;qid=1791318944&amp;s=toys-and-games&amp;sprefix=mg90s%2Bservo%2Ctoys-and-games%2C163&amp;sr=1-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1</t>
   </si>
   <si>
-    <t>Packing Tape</t>
-  </si>
-  <si>
-    <t>https://www.homedepot.com/p/Scotch-1-88-in-x-54-6-yds-Heavy-Duty-Clear-Shipping-and-Packaging-Tape-3850-DC/304884808</t>
-  </si>
-  <si>
     <t>https://www.homedepot.com/p/Loctite-Super-Glue-0-14-oz-Ultra-Gel-Control-Clear-Applicator-1363589/202020461</t>
   </si>
   <si>
@@ -283,10 +277,19 @@
     <t>Cube Holddown Print</t>
   </si>
   <si>
-    <t>MAY NEED TO REPLACE WITH TUBING AND PUT AIRSPEED SENSOR IN FUSELAGE</t>
-  </si>
-  <si>
     <t>made from aluminum l=L bracket</t>
+  </si>
+  <si>
+    <t>Foam Adhesive Tape</t>
+  </si>
+  <si>
+    <t>6 ft</t>
+  </si>
+  <si>
+    <t>https://www.homedepot.com/p/Owens-Corning-HomeSealR-3-in-x-180-ft-Foam-Board-Joint-Tape-1441820/300223152</t>
+  </si>
+  <si>
+    <t>NEED TO FIND THIS</t>
   </si>
 </sst>
 </file>
@@ -348,7 +351,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -370,6 +373,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -743,7 +752,7 @@
       </c>
       <c r="B1" s="4">
         <f>SUM('Per Assembly Cost --&gt;'!B:B)</f>
-        <v>405.05</v>
+        <v>371.64312668463617</v>
       </c>
     </row>
   </sheetData>
@@ -786,7 +795,7 @@
       </c>
       <c r="B2" s="1">
         <f>SUM('Avionics BOM'!D:D)</f>
-        <v>18.420000000000005</v>
+        <v>17.043126684636121</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -795,7 +804,7 @@
       </c>
       <c r="B3" s="1">
         <f>SUM('Structures BOM'!D:D)</f>
-        <v>183.05999999999997</v>
+        <v>151.03000000000003</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -855,7 +864,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>36</v>
@@ -867,12 +876,12 @@
         <v>7.16</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>36</v>
@@ -884,7 +893,7 @@
         <v>1.59</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -901,7 +910,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -918,7 +927,7 @@
         <v>0.4</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -931,9 +940,11 @@
       <c r="C6" s="1">
         <v>1</v>
       </c>
-      <c r="D6" s="5"/>
+      <c r="D6" s="5">
+        <v>2</v>
+      </c>
       <c r="E6" s="6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -950,7 +961,7 @@
         <v>0.99</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -961,18 +972,19 @@
         <v>36</v>
       </c>
       <c r="C8" s="1">
-        <v>100</v>
-      </c>
-      <c r="D8" s="5">
-        <v>7.42</v>
+        <v>30</v>
+      </c>
+      <c r="D8" s="9">
+        <f>30/7.42</f>
+        <v>4.0431266846361185</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>49</v>
@@ -984,12 +996,12 @@
         <v>0.52</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>49</v>
@@ -1001,12 +1013,12 @@
         <v>0.1</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>49</v>
@@ -1018,7 +1030,7 @@
         <v>0.1</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1092,7 +1104,8 @@
         <v>1</v>
       </c>
       <c r="D3" s="5">
-        <v>55.6</v>
+        <f>55.6/2</f>
+        <v>27.8</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>34</v>
@@ -1117,7 +1130,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>36</v>
@@ -1129,7 +1142,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -1202,7 +1215,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>36</v>
@@ -1248,7 +1261,7 @@
         <v>5.98</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -1259,53 +1272,54 @@
         <v>36</v>
       </c>
       <c r="C13" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" s="5">
-        <f>4.48*3</f>
-        <v>13.440000000000001</v>
+        <f>4.48*2</f>
+        <v>8.9600000000000009</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C14" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="1">
-        <v>4.2300000000000004</v>
+        <f>4.23*2</f>
+        <v>8.4600000000000009</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="1">
-        <v>1</v>
-      </c>
-      <c r="D15" s="5">
-        <v>5.98</v>
+      <c r="C15" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D15" s="8">
+        <v>2</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>49</v>
@@ -1317,12 +1331,12 @@
         <v>0.6</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>49</v>
@@ -1334,12 +1348,12 @@
         <v>0.06</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>49</v>
@@ -1351,7 +1365,7 @@
         <v>0.96</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1437,7 +1451,7 @@
         <v>0.33</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -1454,7 +1468,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -1479,11 +1493,11 @@
       <c r="C6" s="1">
         <v>1</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="8">
         <v>16.989999999999998</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -1496,11 +1510,11 @@
       <c r="C7" s="1">
         <v>3</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="8">
         <v>16.989999999999998</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -1517,12 +1531,12 @@
         <v>8.9700000000000006</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>36</v>
@@ -1534,12 +1548,12 @@
         <v>5.52</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>36</v>
@@ -1683,6 +1697,14 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c440327c-db0c-40f7-973b-7bc2ae283ce2" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006F9431A864773547893222757859AEDB" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8d93b3794edbd64c1f12ce1859fb2ebb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c440327c-db0c-40f7-973b-7bc2ae283ce2" xmlns:ns4="3bf09d50-f695-4e18-a2ec-955b0ff6d5dc" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ab198344f7607dd971ab6c53863418c3" ns3:_="" ns4:_="">
     <xsd:import namespace="c440327c-db0c-40f7-973b-7bc2ae283ce2"/>
@@ -1907,14 +1929,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c440327c-db0c-40f7-973b-7bc2ae283ce2" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{140E0E22-42B5-4B4A-934D-04548B25B00B}">
   <ds:schemaRefs>
@@ -1924,6 +1938,23 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F120B44-02FC-4D2A-B0A5-AADC531A6E78}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="c440327c-db0c-40f7-973b-7bc2ae283ce2"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="3bf09d50-f695-4e18-a2ec-955b0ff6d5dc"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92C5615A-B0FE-40B8-955A-C3851BD0A604}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1940,21 +1971,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F120B44-02FC-4D2A-B0A5-AADC531A6E78}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="c440327c-db0c-40f7-973b-7bc2ae283ce2"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="3bf09d50-f695-4e18-a2ec-955b0ff6d5dc"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/CostBreakdown.xlsx
+++ b/CostBreakdown.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jpreisle\Documents\GitHub\451-DBF-Team01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0DE1F80-DDED-4D6C-B75C-BCA8321A3CE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F182D069-968E-4BA0-90A6-10268BE8956E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="831" activeTab="5" xr2:uid="{C684E4FE-65D8-41BB-8319-3046AEA9131B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="831" activeTab="4" xr2:uid="{C684E4FE-65D8-41BB-8319-3046AEA9131B}"/>
   </bookViews>
   <sheets>
     <sheet name="Aircraft Cost Grand Total" sheetId="1" r:id="rId1"/>
@@ -44,13 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="82">
-  <si>
-    <t>GPS Tray</t>
-  </si>
-  <si>
-    <t>Reciever Tray</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="82">
   <si>
     <t>M4 30mm bolt</t>
   </si>
@@ -82,9 +76,6 @@
     <t>Type</t>
   </si>
   <si>
-    <t>Airspeed Sensor Extension Wire</t>
-  </si>
-  <si>
     <t>M4 x 0.7mm washer</t>
   </si>
   <si>
@@ -94,9 +85,6 @@
     <t>Turnigy 4Cell 4000 mAh Battery</t>
   </si>
   <si>
-    <t>2ft x 1.125 x 1.125 in extruded L Aluminum</t>
-  </si>
-  <si>
     <t>1/16 x 1/2 x 1/2 aluminum tube - 6ft</t>
   </si>
   <si>
@@ -106,15 +94,9 @@
     <t xml:space="preserve">Foam Board </t>
   </si>
   <si>
-    <t>Servo Mount</t>
-  </si>
-  <si>
     <t>Control Horns</t>
   </si>
   <si>
-    <t>Aluminum Wire</t>
-  </si>
-  <si>
     <t>Super Glue</t>
   </si>
   <si>
@@ -202,15 +184,6 @@
     <t>https://www.homedepot.com/p/Loctite-Super-Glue-0-14-oz-Ultra-Gel-Control-Clear-Applicator-1363589/202020461</t>
   </si>
   <si>
-    <t>Airspeed Sensor Print</t>
-  </si>
-  <si>
-    <t>Tail Mount Print</t>
-  </si>
-  <si>
-    <t>Wing Dihedral Print</t>
-  </si>
-  <si>
     <t>https://www.homedepot.com/pep/E6000-2-oz-Clear-Adhesive-800432/333376257?g_store=2034&amp;source=shoppingads&amp;locale=en-US&amp;fp=ggl&amp;pla&amp;mtc=SHOPPING-BF-CDP-GGL-D24-024_004_ADHESIVES-NA-NA-NA-PMAX-NA-NA-NA-NA-NBR-NA-NA-NEW-NA_FY25&amp;cm_mmc=SHOPPING-BF-CDP-GGL-D24-024_004_ADHESIVES-NA-NA-NA-PMAX-NA-NA-NA-NA-NBR-NA-NA-NEW-NA_FY25-22204253200--&amp;gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=22204272157&amp;gbraid=0AAAAADq61UcsMashMLoaXkRspH99Y273H&amp;gclid=Cj0KCQjwuJLWBhD_ARIsAIBcRUwCF8rR0SLtACCiYZZMOikqfTXq54H3iKsptby3r_ci7TjzcJ3QqQUaAkesEALw_wcB</t>
   </si>
   <si>
@@ -232,18 +205,9 @@
     <t>https://www.horizonhobby.com/product/wheel-set-3-carbon-z-t-28/EFL1310.html</t>
   </si>
   <si>
-    <t>https://www.horizonhobby.com/product/landing-gear-pawnee-brave-20cc/HAN703509.html</t>
-  </si>
-  <si>
     <t>https://www.amazon.com/Wheel-Assembly-60x25mm-Airplane-Replacement/dp/B019IF9PYE/ref=sr_1_3?crid=1KQYSK0JD4ZZH&amp;dib=eyJ2IjoiMSJ9.8MRt66ofaD-HTPbzJODgG9Qlz2FdPJ91tUSbi09ZX4lr_dHuf2NKoZS7yXkhGvsVO7_WKa_ohMkEsAFLxwt-2Y5LjVyLB1w62LlVb4eYR7M8uBNnncHVAWHKkTz9-JcB18VPXtECOdf-9qaDpfuOhcmxJ7khZT4ibu6UjMTIr81ZbuFd9GNoDpglMVs6y9SRzNO55tNk5TOhnozD2gA5eQOHEgP1Wff9-jEDt36BmgqJ2T0Mya91gIEOvEKWIuxuJ8YbR1seAbvyWi-_NiKZqcaMePTvVA3bQu5wYEkgSmw.9Q_KCk60K2yh_idKVDyKAwH8DcX-mFqYibwQmQG3fHg&amp;dib_tag=se&amp;keywords=hobbypark+tailwheel+assembly&amp;qid=1790866317&amp;sprefix=hobbypark+tailwheel+assembl%2Caps%2C146&amp;sr=8-3</t>
   </si>
   <si>
-    <t>Used Bambu Fillament Prices</t>
-  </si>
-  <si>
-    <t>Motor Cover Print</t>
-  </si>
-  <si>
     <t>Doorhinge</t>
   </si>
   <si>
@@ -256,9 +220,6 @@
     <t>Servo extension wire 24 in</t>
   </si>
   <si>
-    <t>ESC holddown</t>
-  </si>
-  <si>
     <t>https://www.readymaderc.com/products/details/60cm-24-inch-jr-style-22awg-twisted-servo-cable</t>
   </si>
   <si>
@@ -274,12 +235,6 @@
     <t>Rubber Bands</t>
   </si>
   <si>
-    <t>Cube Holddown Print</t>
-  </si>
-  <si>
-    <t>made from aluminum l=L bracket</t>
-  </si>
-  <si>
     <t>Foam Adhesive Tape</t>
   </si>
   <si>
@@ -289,7 +244,52 @@
     <t>https://www.homedepot.com/p/Owens-Corning-HomeSealR-3-in-x-180-ft-Foam-Board-Joint-Tape-1441820/300223152</t>
   </si>
   <si>
-    <t>NEED TO FIND THIS</t>
+    <t>Control Rods</t>
+  </si>
+  <si>
+    <t>LAB STOCK?</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/Standard-Control-17-5x26-Airplane-Replacement/dp/B019I0U8NG</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/uxcell-1-2mm-450mm-Airplane-Replacement/dp/B08K7SFD44/ref=sr_1_5?dib=eyJ2IjoiMSJ9.Xv4Fl3SO-hjoYWOD4Yyq8eCHEQX1GgJdtS7lgvoIz4I4gE9OJmv0Pfpo33JR1AmjuBR1lGVoHsZTS9NA2lB3Db4m8RU_RmouEuuf60fKcDtOCAsT16KfdGIvOWhHHp3vpcK78yX_YpiwUrBfH_uBmARbqz2aTljlkTVo9tz1jM23THeEwLyOJEs9Ox2Oh3rqOMy85hEGvplJPE06rhEegLODbrXBsUrGEKSKdHLd-WQ.E_9_LKhsTYuPwrU52Ke5dijHkXW8E0HgM0qeneplYhY&amp;dib_tag=se&amp;keywords=control%2Brods&amp;qid=1760542926&amp;sr=8-5&amp;th=1hjoYWOD4Yyq8eCHEQX1GgJdtS7lgvoIz4I4gE9OJmv0Pfpo33JR1AmjuBR1lGVoHsZTS9NA2lB3Db4m8RU_RmouEuuf60fKcDtOCAsT16KfdGIvOWhHHp3vpcK78yX_YpiwUrBfH_uBmARbqz2aTljlkTVo9tz1jM23THeEwLyOJEs9Ox2Oh3rqOMy85hEGvplJPE06rhEegLODbrXBsUrGEKSKdHLd-WQ.E_9_LKhsTYuPwrU52Ke5dijHkXW8E0HgM0qeneplYhY&amp;dib_tag=se&amp;keywords=control%2Brods&amp;qid=1760542926&amp;sr=8-5&amp;th=1</t>
+  </si>
+  <si>
+    <t>https://www.horizonhobby.com/product/main-landing-gear-valiant-10cc/HAN508010.html</t>
+  </si>
+  <si>
+    <t>1ft x 1.125 x 1.125 in extruded L Aluminum</t>
+  </si>
+  <si>
+    <t>https://us.store.bambulab.com/products/pla-basic-filament?id=42844629008520</t>
+  </si>
+  <si>
+    <t>Servo Mount PLA</t>
+  </si>
+  <si>
+    <t>Motor Cover Print PLA</t>
+  </si>
+  <si>
+    <t>Wing Dihedral Print PLA</t>
+  </si>
+  <si>
+    <t>Tail Mount Print ABS</t>
+  </si>
+  <si>
+    <t>https://us.store.bambulab.com/products/abs-filament</t>
+  </si>
+  <si>
+    <t>Airspeed Sensor Print PLA</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/12205T76/</t>
   </si>
 </sst>
 </file>
@@ -299,16 +299,8 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -324,7 +316,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -334,6 +326,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -349,7 +347,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -359,7 +357,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -368,24 +366,64 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -748,19 +786,19 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B1" s="4">
         <f>SUM('Per Assembly Cost --&gt;'!B:B)</f>
-        <v>371.64312668463617</v>
+        <v>373.18912668463616</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="lessThan">
       <formula>400</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThan">
       <formula>400</formula>
     </cfRule>
   </conditionalFormatting>
@@ -783,42 +821,42 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B2" s="1">
         <f>SUM('Avionics BOM'!D:D)</f>
-        <v>17.043126684636121</v>
+        <v>14.303126684636119</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B3" s="1">
-        <f>SUM('Structures BOM'!D:D)</f>
-        <v>151.03000000000003</v>
+        <f>SUM('Structures BOM'!E:E)</f>
+        <v>148.08000000000004</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B4" s="1">
         <f>SUM('Mechanisms BOM'!D:D)</f>
-        <v>62.879999999999995</v>
+        <v>70.116</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B5" s="1">
         <f>SUM('Propulsion BOM'!D:D)</f>
@@ -835,39 +873,43 @@
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.28515625" customWidth="1"/>
     <col min="2" max="2" width="10.42578125" style="1" customWidth="1"/>
     <col min="3" max="3" width="9.140625" style="1"/>
     <col min="4" max="4" width="10.28515625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="2"/>
+    <col min="5" max="5" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C2" s="1">
         <v>4</v>
@@ -875,16 +917,19 @@
       <c r="D2" s="1">
         <v>7.16</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C3" s="1">
         <v>1</v>
@@ -892,153 +937,86 @@
       <c r="D3" s="1">
         <v>1.59</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E3" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="C4" s="1">
         <v>1</v>
       </c>
       <c r="D4" s="1">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.99</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="C5" s="1">
-        <v>1</v>
-      </c>
-      <c r="D5" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="D5" s="6">
+        <f>30/7.42</f>
+        <v>4.0431266846361185</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C6" s="1">
         <v>1</v>
       </c>
-      <c r="D6" s="5">
-        <v>2</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="1">
-        <v>1</v>
-      </c>
-      <c r="D7" s="1">
-        <v>0.99</v>
-      </c>
-      <c r="E7" s="3" t="s">
+      <c r="D6" s="1">
+        <v>0.52</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" s="1">
-        <v>30</v>
-      </c>
-      <c r="D8" s="9">
-        <f>30/7.42</f>
-        <v>4.0431266846361185</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" s="1">
-        <v>1</v>
-      </c>
-      <c r="D9" s="1">
-        <v>0.52</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" s="1">
-        <v>1</v>
-      </c>
-      <c r="D10" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>76</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" s="1">
-        <v>2</v>
-      </c>
-      <c r="D11" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
   </sheetData>
+  <conditionalFormatting sqref="E1:E1048576">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+      <formula>"Y"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" location="technical-info-tab" display="https://www.readymaderc.com/products/details/90cm-36in-jr-22awg-servo-cable?gad_source=1&amp;gad_campaignid=17190799136&amp;gbraid=0AAAAADpShvX0lNZ7R-rR4kFhQhZqXsQe4&amp;gclid=Cj0KCQjwuJLWBhD_ARIsAIBcRUwmkykbpZ-Yv1Mmf8ESymVjGKAtao29dLx49Bg4_qsVj1gg-xdR5fkaAsFtEALw_wcB#technical-info-tab" xr:uid="{7C16D964-E42A-476D-8667-EA7484666847}"/>
-    <hyperlink ref="E3" r:id="rId2" xr:uid="{AA186CBF-1F4D-4354-8F4C-254D5CF88C30}"/>
-    <hyperlink ref="E8" r:id="rId3" xr:uid="{1CEF71FE-8065-4760-8150-4B4B1DA37CD5}"/>
-    <hyperlink ref="E7" r:id="rId4" xr:uid="{4EAF33CA-E17C-43DA-8633-E519A1EDF818}"/>
+    <hyperlink ref="F2" r:id="rId1" location="technical-info-tab" display="https://www.readymaderc.com/products/details/90cm-36in-jr-22awg-servo-cable?gad_source=1&amp;gad_campaignid=17190799136&amp;gbraid=0AAAAADpShvX0lNZ7R-rR4kFhQhZqXsQe4&amp;gclid=Cj0KCQjwuJLWBhD_ARIsAIBcRUwmkykbpZ-Yv1Mmf8ESymVjGKAtao29dLx49Bg4_qsVj1gg-xdR5fkaAsFtEALw_wcB#technical-info-tab" xr:uid="{7C16D964-E42A-476D-8667-EA7484666847}"/>
+    <hyperlink ref="F3" r:id="rId2" xr:uid="{AA186CBF-1F4D-4354-8F4C-254D5CF88C30}"/>
+    <hyperlink ref="F5" r:id="rId3" xr:uid="{1CEF71FE-8065-4760-8150-4B4B1DA37CD5}"/>
+    <hyperlink ref="F4" r:id="rId4" xr:uid="{4EAF33CA-E17C-43DA-8633-E519A1EDF818}"/>
+    <hyperlink ref="F6" r:id="rId5" xr:uid="{2C2E3C77-3EE6-4865-850F-8687E6DAA440}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1049,340 +1027,397 @@
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="1"/>
-    <col min="5" max="5" width="9.140625" style="2"/>
+    <col min="4" max="4" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="1"/>
+    <col min="6" max="6" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="5">
         <v>26.26</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C3" s="1">
         <v>1</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="E3" s="7">
         <f>55.6/2</f>
         <v>27.8</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C4" s="1">
         <v>5</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" s="1">
         <v>2.97</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C5" s="1">
         <v>25</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="1">
         <v>4.5999999999999996</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C6" s="1">
         <v>25</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="1">
         <v>5.55</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C7" s="1">
         <v>100</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="1">
         <v>3.93</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C8" s="1">
         <v>25</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="1">
         <v>7.14</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C9" s="1">
         <v>1</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="1">
         <v>24.6</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C10" s="1">
         <v>1</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="1">
         <v>14.27</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F10" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C11" s="1">
         <v>1</v>
       </c>
-      <c r="D11" s="1">
-        <v>6.89</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D11" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="1">
+        <v>3.94</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C12" s="1">
         <v>1</v>
       </c>
-      <c r="D12" s="1">
+      <c r="E12" s="1">
         <v>5.98</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F12" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C13" s="1">
         <v>2</v>
       </c>
-      <c r="D13" s="5">
+      <c r="E13" s="5">
         <f>4.48*2</f>
         <v>8.9600000000000009</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F13" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C14" s="1">
         <v>2</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" s="1">
         <f>4.23*2</f>
         <v>8.4600000000000009</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F14" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E15" s="1">
+        <v>2</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>78</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D15" s="8">
-        <v>2</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>53</v>
-      </c>
       <c r="B16" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C16" s="1">
         <v>1</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E16" s="1">
         <v>0.6</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F16" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C17" s="1">
         <v>1</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E17" s="1">
         <v>0.06</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F17" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C18" s="1">
         <v>1</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E18" s="1">
         <v>0.96</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>64</v>
+      <c r="F18" s="3" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="D1:D1048576">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"Y"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="E11" r:id="rId1" xr:uid="{9B3802E2-0DAA-4495-8E7B-C8A9F6A2FFA8}"/>
-    <hyperlink ref="E9" r:id="rId2" xr:uid="{751BAEB2-26DC-4CAF-8D96-A38FD9446E87}"/>
-    <hyperlink ref="E7" r:id="rId3" xr:uid="{3C1E28BD-D3E4-46AC-A0D8-E327EE566BE4}"/>
-    <hyperlink ref="E8" r:id="rId4" xr:uid="{77BD64C6-BF95-404A-B01F-81F95BAFFFCD}"/>
-    <hyperlink ref="E4" r:id="rId5" xr:uid="{675196D7-5C58-487C-8B15-98E28F3CC124}"/>
-    <hyperlink ref="E6" r:id="rId6" xr:uid="{DAE67438-2EA2-46E6-AE59-3CE1BA52DE6A}"/>
-    <hyperlink ref="E2" r:id="rId7" xr:uid="{20180B92-8ABC-43AC-BBB8-7C093E6B2F3E}"/>
-    <hyperlink ref="E3" r:id="rId8" xr:uid="{EE40E960-AE93-490E-8684-32B42CB94C63}"/>
-    <hyperlink ref="E15" r:id="rId9" xr:uid="{6293C65C-7FE4-4A84-B068-EDC9724F2BCC}"/>
-    <hyperlink ref="E12" r:id="rId10" xr:uid="{4107E890-CEA7-4F2F-B7A9-E682D7C164AD}"/>
-    <hyperlink ref="E14" r:id="rId11" xr:uid="{A91A1DE5-4331-40CB-B90C-715E0BCCB855}"/>
-    <hyperlink ref="E10" r:id="rId12" xr:uid="{A329B7F4-245D-42E5-AACE-0CD364DDF33B}"/>
-    <hyperlink ref="E5" r:id="rId13" xr:uid="{410C3B3D-E226-4918-926D-2343FE7E95FB}"/>
+    <hyperlink ref="F11" r:id="rId1" xr:uid="{9B3802E2-0DAA-4495-8E7B-C8A9F6A2FFA8}"/>
+    <hyperlink ref="F9" r:id="rId2" xr:uid="{751BAEB2-26DC-4CAF-8D96-A38FD9446E87}"/>
+    <hyperlink ref="F7" r:id="rId3" xr:uid="{3C1E28BD-D3E4-46AC-A0D8-E327EE566BE4}"/>
+    <hyperlink ref="F8" r:id="rId4" xr:uid="{77BD64C6-BF95-404A-B01F-81F95BAFFFCD}"/>
+    <hyperlink ref="F4" r:id="rId5" xr:uid="{675196D7-5C58-487C-8B15-98E28F3CC124}"/>
+    <hyperlink ref="F6" r:id="rId6" xr:uid="{DAE67438-2EA2-46E6-AE59-3CE1BA52DE6A}"/>
+    <hyperlink ref="F2" r:id="rId7" xr:uid="{20180B92-8ABC-43AC-BBB8-7C093E6B2F3E}"/>
+    <hyperlink ref="F3" r:id="rId8" xr:uid="{EE40E960-AE93-490E-8684-32B42CB94C63}"/>
+    <hyperlink ref="F15" r:id="rId9" xr:uid="{6293C65C-7FE4-4A84-B068-EDC9724F2BCC}"/>
+    <hyperlink ref="F12" r:id="rId10" xr:uid="{4107E890-CEA7-4F2F-B7A9-E682D7C164AD}"/>
+    <hyperlink ref="F14" r:id="rId11" xr:uid="{A91A1DE5-4331-40CB-B90C-715E0BCCB855}"/>
+    <hyperlink ref="F10" r:id="rId12" xr:uid="{A329B7F4-245D-42E5-AACE-0CD364DDF33B}"/>
+    <hyperlink ref="F5" r:id="rId13" xr:uid="{410C3B3D-E226-4918-926D-2343FE7E95FB}"/>
+    <hyperlink ref="F17" r:id="rId14" xr:uid="{52B7F4D8-0087-463C-BADE-67E924F10F6E}"/>
+    <hyperlink ref="F18" r:id="rId15" xr:uid="{9522780B-6A52-4DDE-B8E6-B5235444D7F4}"/>
+    <hyperlink ref="F16" r:id="rId16" xr:uid="{C7A4C835-2651-4775-9B34-D0ACB86D0FCC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1393,39 +1428,43 @@
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.85546875" style="1" customWidth="1"/>
     <col min="3" max="3" width="9.140625" style="1"/>
     <col min="4" max="4" width="10.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="2"/>
+    <col min="5" max="5" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C2" s="1">
         <v>4</v>
@@ -1433,16 +1472,19 @@
       <c r="D2" s="1">
         <v>13.88</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E2" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C3" s="1">
         <v>4</v>
@@ -1450,79 +1492,99 @@
       <c r="D3" s="1">
         <v>0.33</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E3" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C4" s="1">
         <v>4</v>
       </c>
       <c r="D4" s="1">
-        <v>0</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2.99</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C5" s="1">
-        <v>1</v>
-      </c>
-      <c r="D5" s="5"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="D5" s="1">
+        <v>6.2759999999999998</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="8">
-        <v>16.989999999999998</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>14.99</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C7" s="1">
         <v>3</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="7">
         <v>16.989999999999998</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E7" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C8" s="1">
         <v>1</v>
@@ -1530,16 +1592,19 @@
       <c r="D8" s="1">
         <v>8.9700000000000006</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E8" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C9" s="1">
         <v>3</v>
@@ -1547,30 +1612,46 @@
       <c r="D9" s="1">
         <v>5.52</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E9" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C10" s="1">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="D10" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="E10" s="7"/>
+        <v>0.17</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>81</v>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="E1:E1048576">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>"Y"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="E7" r:id="rId1" xr:uid="{53C4CC5E-18BB-493C-B4BF-A5DBA279DD54}"/>
-    <hyperlink ref="E6" r:id="rId2" xr:uid="{0004C175-5738-4B8F-BD83-32A5A30FB28E}"/>
-    <hyperlink ref="E9" r:id="rId3" xr:uid="{8D7210AE-DB3A-46B9-AA95-7FD3E6229A86}"/>
+    <hyperlink ref="F7" r:id="rId1" xr:uid="{53C4CC5E-18BB-493C-B4BF-A5DBA279DD54}"/>
+    <hyperlink ref="F6" r:id="rId2" xr:uid="{0004C175-5738-4B8F-BD83-32A5A30FB28E}"/>
+    <hyperlink ref="F9" r:id="rId3" xr:uid="{8D7210AE-DB3A-46B9-AA95-7FD3E6229A86}"/>
+    <hyperlink ref="F4" r:id="rId4" xr:uid="{0E92F0AD-782A-4CF6-8DF2-62BFB580A776}"/>
+    <hyperlink ref="F3" r:id="rId5" xr:uid="{7B1E3156-A427-4EE6-BDAE-640964CFC534}"/>
+    <hyperlink ref="F10" r:id="rId6" xr:uid="{4D5B5F44-6C1C-49C0-8972-E0BE3BA5E7E1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1581,39 +1662,42 @@
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.5703125" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="2"/>
+    <col min="4" max="5" width="12.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
       <c r="B2" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
@@ -1621,16 +1705,19 @@
       <c r="D2" s="1">
         <v>3.64</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E2" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C3" s="1">
         <v>1</v>
@@ -1638,16 +1725,19 @@
       <c r="D3" s="1">
         <v>57.99</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E3" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C4" s="1">
         <v>1</v>
@@ -1655,16 +1745,19 @@
       <c r="D4" s="1">
         <v>38.49</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C5" s="1">
         <v>1</v>
@@ -1672,39 +1765,30 @@
       <c r="D5" s="1">
         <v>40.57</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>44</v>
+      <c r="E5" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="E1:E1048576">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"Y"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" xr:uid="{F52A4918-E897-4C4E-897E-D5215E045CA6}"/>
-    <hyperlink ref="E3" r:id="rId2" xr:uid="{33A92E14-CC68-4656-B82C-8BE565F4FCFD}"/>
-    <hyperlink ref="E4" r:id="rId3" xr:uid="{50C17E5A-DE64-49D2-A6A1-C7139C62E0DA}"/>
-    <hyperlink ref="E5" r:id="rId4" xr:uid="{B212F068-A19C-47FA-90E5-D3A0FCB21397}"/>
+    <hyperlink ref="F2" r:id="rId1" xr:uid="{F52A4918-E897-4C4E-897E-D5215E045CA6}"/>
+    <hyperlink ref="F3" r:id="rId2" xr:uid="{33A92E14-CC68-4656-B82C-8BE565F4FCFD}"/>
+    <hyperlink ref="F4" r:id="rId3" xr:uid="{50C17E5A-DE64-49D2-A6A1-C7139C62E0DA}"/>
+    <hyperlink ref="F5" r:id="rId4" xr:uid="{B212F068-A19C-47FA-90E5-D3A0FCB21397}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c440327c-db0c-40f7-973b-7bc2ae283ce2" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006F9431A864773547893222757859AEDB" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8d93b3794edbd64c1f12ce1859fb2ebb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c440327c-db0c-40f7-973b-7bc2ae283ce2" xmlns:ns4="3bf09d50-f695-4e18-a2ec-955b0ff6d5dc" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ab198344f7607dd971ab6c53863418c3" ns3:_="" ns4:_="">
     <xsd:import namespace="c440327c-db0c-40f7-973b-7bc2ae283ce2"/>
@@ -1929,10 +2013,38 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c440327c-db0c-40f7-973b-7bc2ae283ce2" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{140E0E22-42B5-4B4A-934D-04548B25B00B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92C5615A-B0FE-40B8-955A-C3851BD0A604}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="c440327c-db0c-40f7-973b-7bc2ae283ce2"/>
+    <ds:schemaRef ds:uri="3bf09d50-f695-4e18-a2ec-955b0ff6d5dc"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1955,20 +2067,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92C5615A-B0FE-40B8-955A-C3851BD0A604}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{140E0E22-42B5-4B4A-934D-04548B25B00B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="c440327c-db0c-40f7-973b-7bc2ae283ce2"/>
-    <ds:schemaRef ds:uri="3bf09d50-f695-4e18-a2ec-955b0ff6d5dc"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/CostBreakdown.xlsx
+++ b/CostBreakdown.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jpreisle\Documents\GitHub\451-DBF-Team01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F182D069-968E-4BA0-90A6-10268BE8956E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3449F9D-46B8-46FF-A78A-F530D8293688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="831" activeTab="4" xr2:uid="{C684E4FE-65D8-41BB-8319-3046AEA9131B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="831" activeTab="2" xr2:uid="{C684E4FE-65D8-41BB-8319-3046AEA9131B}"/>
   </bookViews>
   <sheets>
     <sheet name="Aircraft Cost Grand Total" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="83">
   <si>
     <t>M4 30mm bolt</t>
   </si>
@@ -97,9 +97,6 @@
     <t>Control Horns</t>
   </si>
   <si>
-    <t>Super Glue</t>
-  </si>
-  <si>
     <t>Main Landing Gear</t>
   </si>
   <si>
@@ -163,9 +160,6 @@
     <t>https://hobbyking.com/en_us/turnigy-battery-4000mah-4s-30c-lipo-pack-xt-60.html?srsltid=AU7gw4WVGopDsORjxCL-xylPi1hT8fcP1h7w3tHevpSY-TgKOw5vp4lY</t>
   </si>
   <si>
-    <t>Wood Glue</t>
-  </si>
-  <si>
     <t>Battery Strap</t>
   </si>
   <si>
@@ -181,21 +175,9 @@
     <t>https://www.amazon.com/Miuzei-Geared-Helicopter-Arduino-Project/dp/B0CP98TZJ2/ref=sr_1_1_sspa?crid=3UWKW3AUXSAKT&amp;dib=eyJ2IjoiMSJ9.EdycfDxnDtcyy4IWKKo05CT4vxdxksMXHI4KVwvilewG4LFzZMiLD-SKTNAvfkn4n3bvzzknFtE5jqLS00GcsR7QSNBrrplhBsFkdc5C7iyFYKU1_Vb1mhk3C7o5-PxM_34Q6HMkAV_urpdOH6vLjHjf_mxsGFtruVyux7qyyMBxdQ_rSkVFyQGAwCDKCI88NTD0eIyd3TvFcExUWLg1DTeMO4Dq4BhMZDTM3cre_Y5T8fpD7C6svcrSYhyshFkTslJFxTQ2ECM_4oD4NXBrL1JYotARBhRZd5SXqmh1hWg.VKHwGgs_7fH_kPtCF2In0AiV3-5WYmgh5fjs7UV6F28&amp;dib_tag=se&amp;keywords=mg90s%2Bservo&amp;qid=1791318944&amp;s=toys-and-games&amp;sprefix=mg90s%2Bservo%2Ctoys-and-games%2C163&amp;sr=1-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1</t>
   </si>
   <si>
-    <t>https://www.homedepot.com/p/Loctite-Super-Glue-0-14-oz-Ultra-Gel-Control-Clear-Applicator-1363589/202020461</t>
-  </si>
-  <si>
-    <t>https://www.homedepot.com/pep/E6000-2-oz-Clear-Adhesive-800432/333376257?g_store=2034&amp;source=shoppingads&amp;locale=en-US&amp;fp=ggl&amp;pla&amp;mtc=SHOPPING-BF-CDP-GGL-D24-024_004_ADHESIVES-NA-NA-NA-PMAX-NA-NA-NA-NA-NBR-NA-NA-NEW-NA_FY25&amp;cm_mmc=SHOPPING-BF-CDP-GGL-D24-024_004_ADHESIVES-NA-NA-NA-PMAX-NA-NA-NA-NA-NBR-NA-NA-NEW-NA_FY25-22204253200--&amp;gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=22204272157&amp;gbraid=0AAAAADq61UcsMashMLoaXkRspH99Y273H&amp;gclid=Cj0KCQjwuJLWBhD_ARIsAIBcRUwCF8rR0SLtACCiYZZMOikqfTXq54H3iKsptby3r_ci7TjzcJ3QqQUaAkesEALw_wcB</t>
-  </si>
-  <si>
     <t>1/16 x 1/2 x 1/2 aluminum tube - 3ft</t>
   </si>
   <si>
-    <t>Aluminum Tube 6 in (Spacer</t>
-  </si>
-  <si>
-    <t>https://www.mcmaster.com/products/8978k911/</t>
-  </si>
-  <si>
     <t>https://www.mcmaster.com/products/91274a122/</t>
   </si>
   <si>
@@ -208,9 +190,6 @@
     <t>https://www.amazon.com/Wheel-Assembly-60x25mm-Airplane-Replacement/dp/B019IF9PYE/ref=sr_1_3?crid=1KQYSK0JD4ZZH&amp;dib=eyJ2IjoiMSJ9.8MRt66ofaD-HTPbzJODgG9Qlz2FdPJ91tUSbi09ZX4lr_dHuf2NKoZS7yXkhGvsVO7_WKa_ohMkEsAFLxwt-2Y5LjVyLB1w62LlVb4eYR7M8uBNnncHVAWHKkTz9-JcB18VPXtECOdf-9qaDpfuOhcmxJ7khZT4ibu6UjMTIr81ZbuFd9GNoDpglMVs6y9SRzNO55tNk5TOhnozD2gA5eQOHEgP1Wff9-jEDt36BmgqJ2T0Mya91gIEOvEKWIuxuJ8YbR1seAbvyWi-_NiKZqcaMePTvVA3bQu5wYEkgSmw.9Q_KCk60K2yh_idKVDyKAwH8DcX-mFqYibwQmQG3fHg&amp;dib_tag=se&amp;keywords=hobbypark+tailwheel+assembly&amp;qid=1790866317&amp;sprefix=hobbypark+tailwheel+assembl%2Caps%2C146&amp;sr=8-3</t>
   </si>
   <si>
-    <t>Doorhinge</t>
-  </si>
-  <si>
     <t>Servo Extension Wires 36 in</t>
   </si>
   <si>
@@ -223,9 +202,6 @@
     <t>https://www.readymaderc.com/products/details/60cm-24-inch-jr-style-22awg-twisted-servo-cable</t>
   </si>
   <si>
-    <t>https://www.mcmaster.com/16175A561/</t>
-  </si>
-  <si>
     <t>https://www.mcmaster.com/2113N16/</t>
   </si>
   <si>
@@ -238,9 +214,6 @@
     <t>Foam Adhesive Tape</t>
   </si>
   <si>
-    <t>6 ft</t>
-  </si>
-  <si>
     <t>https://www.homedepot.com/p/Owens-Corning-HomeSealR-3-in-x-180-ft-Foam-Board-Joint-Tape-1441820/300223152</t>
   </si>
   <si>
@@ -290,6 +263,36 @@
   </si>
   <si>
     <t>https://www.mcmaster.com/12205T76/</t>
+  </si>
+  <si>
+    <t>12 ft</t>
+  </si>
+  <si>
+    <t>Dowels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorilla Wood Glue </t>
+  </si>
+  <si>
+    <t>Gorilla Super Glue</t>
+  </si>
+  <si>
+    <t>https://www.homedepot.com/p/Gorilla-8-oz-Wood-Glue-Natural-62000/100672167</t>
+  </si>
+  <si>
+    <t>6 oz</t>
+  </si>
+  <si>
+    <t>https://www.homedepot.com/p/Gorilla-25g-Super-Glue-XL-7400202/329800516</t>
+  </si>
+  <si>
+    <t>15g</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/94669A135/</t>
+  </si>
+  <si>
+    <t>Aluminum 40mm x 8 mm OD Spacer</t>
   </si>
 </sst>
 </file>
@@ -316,18 +319,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -349,7 +346,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -363,27 +360,70 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="10">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -790,15 +830,15 @@
       </c>
       <c r="B1" s="4">
         <f>SUM('Per Assembly Cost --&gt;'!B:B)</f>
-        <v>373.18912668463616</v>
+        <v>355.51941778975743</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="lessThan">
       <formula>400</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="greaterThan">
       <formula>400</formula>
     </cfRule>
   </conditionalFormatting>
@@ -821,7 +861,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
@@ -829,34 +869,34 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B2" s="1">
+        <v>31</v>
+      </c>
+      <c r="B2" s="5">
         <f>SUM('Avionics BOM'!D:D)</f>
-        <v>14.303126684636119</v>
+        <v>14.695417789757411</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B3" s="1">
-        <f>SUM('Structures BOM'!E:E)</f>
-        <v>148.08000000000004</v>
+        <f>SUM('Structures BOM'!D:D)</f>
+        <v>146.80300000000003</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B4" s="1">
         <f>SUM('Mechanisms BOM'!D:D)</f>
-        <v>70.116</v>
+        <v>53.330999999999996</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B5" s="1">
         <f>SUM('Propulsion BOM'!D:D)</f>
@@ -898,7 +938,7 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
@@ -906,10 +946,10 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C2" s="1">
         <v>4</v>
@@ -918,18 +958,18 @@
         <v>7.16</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C3" s="1">
         <v>1</v>
@@ -938,76 +978,82 @@
         <v>1.59</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C4" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4" s="1">
-        <v>0.99</v>
+        <f>3*0.99</f>
+        <v>2.9699999999999998</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C5" s="1">
-        <v>30</v>
-      </c>
-      <c r="D5" s="6">
-        <f>30/7.42</f>
-        <v>4.0431266846361185</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>68</v>
+        <v>20</v>
+      </c>
+      <c r="D5" s="5">
+        <f>20/7.42</f>
+        <v>2.6954177897574123</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C6" s="1">
         <v>1</v>
       </c>
-      <c r="D6" s="1">
-        <v>0.52</v>
+      <c r="D6" s="7">
+        <v>0.28000000000000003</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E1:E1048576">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+  <conditionalFormatting sqref="E1:E5 E7:E1048576">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+      <formula>"Y"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E6">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
       <formula>"Y"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1027,14 +1073,14 @@
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="1"/>
+    <col min="4" max="4" width="9.140625" style="1"/>
+    <col min="5" max="5" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.140625" style="2"/>
   </cols>
   <sheetData>
@@ -1049,10 +1095,10 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
@@ -1063,19 +1109,19 @@
         <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E2" s="5">
+      <c r="D2" s="7">
         <v>26.26</v>
       </c>
+      <c r="E2" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="F2" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1083,20 +1129,20 @@
         <v>15</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C3" s="1">
         <v>1</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E3" s="7">
+      <c r="D3" s="7">
         <f>55.6/2</f>
         <v>27.8</v>
       </c>
+      <c r="E3" s="1" t="s">
+        <v>59</v>
+      </c>
       <c r="F3" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1104,39 +1150,39 @@
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C4" s="1">
         <v>5</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E4" s="1">
+      <c r="D4" s="1">
         <v>2.97</v>
       </c>
+      <c r="E4" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="F4" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C5" s="1">
         <v>25</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E5" s="1">
+      <c r="D5" s="1">
         <v>4.5999999999999996</v>
       </c>
+      <c r="E5" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="F5" s="3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1144,19 +1190,19 @@
         <v>1</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C6" s="1">
         <v>25</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E6" s="1">
+      <c r="D6" s="1">
         <v>5.55</v>
       </c>
+      <c r="E6" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="F6" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1164,19 +1210,19 @@
         <v>10</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C7" s="1">
         <v>100</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E7" s="1">
+      <c r="D7" s="1">
         <v>3.93</v>
       </c>
+      <c r="E7" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="F7" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1184,19 +1230,19 @@
         <v>11</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C8" s="1">
         <v>25</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E8" s="1">
+      <c r="D8" s="1">
         <v>7.14</v>
       </c>
+      <c r="E8" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="F8" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1204,220 +1250,262 @@
         <v>13</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C9" s="1">
         <v>1</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E9" s="1">
+      <c r="D9" s="1">
         <v>24.6</v>
       </c>
+      <c r="E9" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="F9" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C10" s="1">
         <v>1</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E10" s="1">
+      <c r="D10" s="1">
         <v>14.27</v>
       </c>
+      <c r="E10" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="F10" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="1">
         <v>1</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E11" s="1">
+      <c r="D11" s="1">
         <v>3.94</v>
       </c>
+      <c r="E11" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="F11" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="1">
-        <v>1</v>
-      </c>
-      <c r="E12" s="1">
-        <v>5.98</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>45</v>
+        <v>29</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" s="10">
+        <f>4.98/8*6</f>
+        <v>3.7350000000000003</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="1">
-        <v>2</v>
-      </c>
-      <c r="E13" s="5">
-        <f>4.48*2</f>
-        <v>8.9600000000000009</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>46</v>
+        <v>29</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D13" s="10">
+        <f>9.98*0.6</f>
+        <v>5.9880000000000004</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C14" s="1">
-        <v>2</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E14" s="1">
-        <f>4.23*2</f>
-        <v>8.4600000000000009</v>
+        <v>4</v>
+      </c>
+      <c r="D14" s="1">
+        <f>2.46*4</f>
+        <v>9.84</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>49</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E15" s="1">
-        <v>2</v>
+        <v>73</v>
+      </c>
+      <c r="D15" s="1">
+        <v>4.07</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C16" s="1">
         <v>1</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E16" s="1">
-        <v>0.6</v>
+      <c r="D16" s="7">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C17" s="1">
         <v>1</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E17" s="1">
+      <c r="D17" s="7">
         <v>0.06</v>
       </c>
+      <c r="E17" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="F17" s="3" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C18" s="1">
         <v>1</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E18" s="1">
-        <v>0.96</v>
+      <c r="D18" s="7">
+        <v>0.91</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="F18" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>74</v>
       </c>
+      <c r="B19" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="1">
+        <v>4</v>
+      </c>
+      <c r="D19" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>70</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D1:D1048576">
+  <conditionalFormatting sqref="E1:E15 E20:E1048576">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
+      <formula>"Y"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E16:E17">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
+      <formula>"Y"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E18">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+      <formula>"Y"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E19">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Y"</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="F11" r:id="rId1" xr:uid="{9B3802E2-0DAA-4495-8E7B-C8A9F6A2FFA8}"/>
-    <hyperlink ref="F9" r:id="rId2" xr:uid="{751BAEB2-26DC-4CAF-8D96-A38FD9446E87}"/>
-    <hyperlink ref="F7" r:id="rId3" xr:uid="{3C1E28BD-D3E4-46AC-A0D8-E327EE566BE4}"/>
-    <hyperlink ref="F8" r:id="rId4" xr:uid="{77BD64C6-BF95-404A-B01F-81F95BAFFFCD}"/>
-    <hyperlink ref="F4" r:id="rId5" xr:uid="{675196D7-5C58-487C-8B15-98E28F3CC124}"/>
-    <hyperlink ref="F6" r:id="rId6" xr:uid="{DAE67438-2EA2-46E6-AE59-3CE1BA52DE6A}"/>
-    <hyperlink ref="F2" r:id="rId7" xr:uid="{20180B92-8ABC-43AC-BBB8-7C093E6B2F3E}"/>
+    <hyperlink ref="F16" r:id="rId1" xr:uid="{C7A4C835-2651-4775-9B34-D0ACB86D0FCC}"/>
+    <hyperlink ref="F18" r:id="rId2" xr:uid="{9522780B-6A52-4DDE-B8E6-B5235444D7F4}"/>
+    <hyperlink ref="F17" r:id="rId3" xr:uid="{52B7F4D8-0087-463C-BADE-67E924F10F6E}"/>
+    <hyperlink ref="F5" r:id="rId4" xr:uid="{410C3B3D-E226-4918-926D-2343FE7E95FB}"/>
+    <hyperlink ref="F10" r:id="rId5" xr:uid="{A329B7F4-245D-42E5-AACE-0CD364DDF33B}"/>
+    <hyperlink ref="F14" r:id="rId6" xr:uid="{A91A1DE5-4331-40CB-B90C-715E0BCCB855}"/>
+    <hyperlink ref="F15" r:id="rId7" xr:uid="{6293C65C-7FE4-4A84-B068-EDC9724F2BCC}"/>
     <hyperlink ref="F3" r:id="rId8" xr:uid="{EE40E960-AE93-490E-8684-32B42CB94C63}"/>
-    <hyperlink ref="F15" r:id="rId9" xr:uid="{6293C65C-7FE4-4A84-B068-EDC9724F2BCC}"/>
-    <hyperlink ref="F12" r:id="rId10" xr:uid="{4107E890-CEA7-4F2F-B7A9-E682D7C164AD}"/>
-    <hyperlink ref="F14" r:id="rId11" xr:uid="{A91A1DE5-4331-40CB-B90C-715E0BCCB855}"/>
-    <hyperlink ref="F10" r:id="rId12" xr:uid="{A329B7F4-245D-42E5-AACE-0CD364DDF33B}"/>
-    <hyperlink ref="F5" r:id="rId13" xr:uid="{410C3B3D-E226-4918-926D-2343FE7E95FB}"/>
-    <hyperlink ref="F17" r:id="rId14" xr:uid="{52B7F4D8-0087-463C-BADE-67E924F10F6E}"/>
-    <hyperlink ref="F18" r:id="rId15" xr:uid="{9522780B-6A52-4DDE-B8E6-B5235444D7F4}"/>
-    <hyperlink ref="F16" r:id="rId16" xr:uid="{C7A4C835-2651-4775-9B34-D0ACB86D0FCC}"/>
+    <hyperlink ref="F2" r:id="rId9" xr:uid="{20180B92-8ABC-43AC-BBB8-7C093E6B2F3E}"/>
+    <hyperlink ref="F6" r:id="rId10" xr:uid="{DAE67438-2EA2-46E6-AE59-3CE1BA52DE6A}"/>
+    <hyperlink ref="F4" r:id="rId11" xr:uid="{675196D7-5C58-487C-8B15-98E28F3CC124}"/>
+    <hyperlink ref="F8" r:id="rId12" xr:uid="{77BD64C6-BF95-404A-B01F-81F95BAFFFCD}"/>
+    <hyperlink ref="F7" r:id="rId13" xr:uid="{3C1E28BD-D3E4-46AC-A0D8-E327EE566BE4}"/>
+    <hyperlink ref="F9" r:id="rId14" xr:uid="{751BAEB2-26DC-4CAF-8D96-A38FD9446E87}"/>
+    <hyperlink ref="F11" r:id="rId15" xr:uid="{9B3802E2-0DAA-4495-8E7B-C8A9F6A2FFA8}"/>
+    <hyperlink ref="F19" r:id="rId16" xr:uid="{8B7798E1-B9EF-4C27-8F45-57F8754CF6C6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1428,7 +1516,7 @@
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.7109375" bestFit="1" customWidth="1"/>
@@ -1453,7 +1541,7 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
@@ -1461,10 +1549,10 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C2" s="1">
         <v>4</v>
@@ -1473,30 +1561,30 @@
         <v>13.88</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C3" s="1">
-        <v>4</v>
-      </c>
-      <c r="D3" s="1">
-        <v>0.33</v>
+        <v>2</v>
+      </c>
+      <c r="D3" s="7">
+        <v>0.11</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1504,7 +1592,7 @@
         <v>16</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C4" s="1">
         <v>4</v>
@@ -1513,18 +1601,18 @@
         <v>2.99</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C5" s="1">
         <v>4</v>
@@ -1532,59 +1620,60 @@
       <c r="D5" s="1">
         <v>6.2759999999999998</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>68</v>
+      <c r="E5" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C6" s="1">
         <v>1</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="6">
         <v>14.99</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C7" s="1">
-        <v>3</v>
-      </c>
-      <c r="D7" s="7">
-        <v>16.989999999999998</v>
+        <v>2</v>
+      </c>
+      <c r="D7" s="10">
+        <f>11.99/2</f>
+        <v>5.9950000000000001</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C8" s="1">
         <v>1</v>
@@ -1593,10 +1682,10 @@
         <v>8.9700000000000006</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1604,39 +1693,19 @@
         <v>54</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C9" s="1">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D9" s="1">
-        <v>5.52</v>
+        <v>0.12</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F9" s="3" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>62</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="1">
-        <v>30</v>
-      </c>
-      <c r="D10" s="1">
-        <v>0.17</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>81</v>
+      <c r="F9" s="8" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1648,10 +1717,9 @@
   <hyperlinks>
     <hyperlink ref="F7" r:id="rId1" xr:uid="{53C4CC5E-18BB-493C-B4BF-A5DBA279DD54}"/>
     <hyperlink ref="F6" r:id="rId2" xr:uid="{0004C175-5738-4B8F-BD83-32A5A30FB28E}"/>
-    <hyperlink ref="F9" r:id="rId3" xr:uid="{8D7210AE-DB3A-46B9-AA95-7FD3E6229A86}"/>
-    <hyperlink ref="F4" r:id="rId4" xr:uid="{0E92F0AD-782A-4CF6-8DF2-62BFB580A776}"/>
-    <hyperlink ref="F3" r:id="rId5" xr:uid="{7B1E3156-A427-4EE6-BDAE-640964CFC534}"/>
-    <hyperlink ref="F10" r:id="rId6" xr:uid="{4D5B5F44-6C1C-49C0-8972-E0BE3BA5E7E1}"/>
+    <hyperlink ref="F4" r:id="rId3" xr:uid="{0E92F0AD-782A-4CF6-8DF2-62BFB580A776}"/>
+    <hyperlink ref="F3" r:id="rId4" xr:uid="{7B1E3156-A427-4EE6-BDAE-640964CFC534}"/>
+    <hyperlink ref="F9" r:id="rId5" xr:uid="{4D5B5F44-6C1C-49C0-8972-E0BE3BA5E7E1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1686,7 +1754,7 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
@@ -1697,7 +1765,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
@@ -1706,10 +1774,10 @@
         <v>3.64</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1717,7 +1785,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C3" s="1">
         <v>1</v>
@@ -1726,10 +1794,10 @@
         <v>57.99</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1737,7 +1805,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C4" s="1">
         <v>1</v>
@@ -1746,10 +1814,10 @@
         <v>38.49</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1757,7 +1825,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C5" s="1">
         <v>1</v>
@@ -1766,10 +1834,10 @@
         <v>40.57</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1789,6 +1857,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c440327c-db0c-40f7-973b-7bc2ae283ce2" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006F9431A864773547893222757859AEDB" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8d93b3794edbd64c1f12ce1859fb2ebb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c440327c-db0c-40f7-973b-7bc2ae283ce2" xmlns:ns4="3bf09d50-f695-4e18-a2ec-955b0ff6d5dc" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ab198344f7607dd971ab6c53863418c3" ns3:_="" ns4:_="">
     <xsd:import namespace="c440327c-db0c-40f7-973b-7bc2ae283ce2"/>
@@ -2013,14 +2089,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c440327c-db0c-40f7-973b-7bc2ae283ce2" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -2031,6 +2099,23 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F120B44-02FC-4D2A-B0A5-AADC531A6E78}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="c440327c-db0c-40f7-973b-7bc2ae283ce2"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="3bf09d50-f695-4e18-a2ec-955b0ff6d5dc"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92C5615A-B0FE-40B8-955A-C3851BD0A604}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2049,23 +2134,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F120B44-02FC-4D2A-B0A5-AADC531A6E78}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="c440327c-db0c-40f7-973b-7bc2ae283ce2"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="3bf09d50-f695-4e18-a2ec-955b0ff6d5dc"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{140E0E22-42B5-4B4A-934D-04548B25B00B}">
   <ds:schemaRefs>

--- a/CostBreakdown.xlsx
+++ b/CostBreakdown.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jpreisle\Documents\GitHub\451-DBF-Team01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jpreisle\Documents\Visual Studio\Git\451-DBF-Team01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3449F9D-46B8-46FF-A78A-F530D8293688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{812E67BB-1D44-4D6D-9542-41B82AC33CDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="831" activeTab="2" xr2:uid="{C684E4FE-65D8-41BB-8319-3046AEA9131B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="831" activeTab="5" xr2:uid="{C684E4FE-65D8-41BB-8319-3046AEA9131B}"/>
   </bookViews>
   <sheets>
     <sheet name="Aircraft Cost Grand Total" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="93">
   <si>
     <t>M4 30mm bolt</t>
   </si>
@@ -293,6 +293,36 @@
   </si>
   <si>
     <t>Aluminum 40mm x 8 mm OD Spacer</t>
+  </si>
+  <si>
+    <t>3M Pads</t>
+  </si>
+  <si>
+    <t>change to PETG</t>
+  </si>
+  <si>
+    <t>find cost and verify quantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">single sided velcro </t>
+  </si>
+  <si>
+    <t>Duct Tape</t>
+  </si>
+  <si>
+    <t>Bambu Skewers</t>
+  </si>
+  <si>
+    <t>check If we can use this glue</t>
+  </si>
+  <si>
+    <t>maybe use easy connectors instead</t>
+  </si>
+  <si>
+    <t>check 3520/12</t>
+  </si>
+  <si>
+    <t>check 11x8E</t>
   </si>
 </sst>
 </file>
@@ -302,7 +332,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -314,6 +344,13 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -346,7 +383,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -366,64 +403,19 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="6">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -818,27 +810,27 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" customWidth="1"/>
+    <col min="2" max="2" width="16.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="4">
         <f>SUM('Per Assembly Cost --&gt;'!B:B)</f>
-        <v>355.51941778975743</v>
+        <v>361.51941778975743</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="lessThan">
       <formula>400</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThan">
       <formula>400</formula>
     </cfRule>
   </conditionalFormatting>
@@ -853,13 +845,13 @@
     <tabColor theme="1"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.28515625" customWidth="1"/>
-    <col min="2" max="2" width="22.85546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="23.33203125" customWidth="1"/>
+    <col min="2" max="2" width="22.88671875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
@@ -867,7 +859,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>31</v>
       </c>
@@ -876,16 +868,16 @@
         <v>14.695417789757411</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>32</v>
       </c>
       <c r="B3" s="1">
         <f>SUM('Structures BOM'!D:D)</f>
-        <v>146.80300000000003</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>152.80300000000003</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -894,7 +886,7 @@
         <v>53.330999999999996</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>34</v>
       </c>
@@ -914,17 +906,17 @@
     <tabColor theme="0"/>
   </sheetPr>
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.28515625" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" style="1"/>
-    <col min="4" max="4" width="10.28515625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="2"/>
+    <col min="1" max="1" width="30.33203125" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" style="1"/>
+    <col min="4" max="4" width="10.33203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -944,7 +936,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>48</v>
       </c>
@@ -958,13 +950,13 @@
         <v>7.16</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>50</v>
       </c>
@@ -978,13 +970,13 @@
         <v>1.59</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>38</v>
       </c>
@@ -1005,7 +997,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>39</v>
       </c>
@@ -1026,7 +1018,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>71</v>
       </c>
@@ -1036,7 +1028,7 @@
       <c r="C6" s="1">
         <v>1</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="1">
         <v>0.28000000000000003</v>
       </c>
       <c r="E6" s="1" t="s">
@@ -1047,13 +1039,8 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E1:E5 E7:E1048576">
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
-      <formula>"Y"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
+  <conditionalFormatting sqref="E1:E1048576">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"Y"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1073,18 +1060,18 @@
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="1"/>
-    <col min="5" max="5" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="2"/>
+    <col min="1" max="1" width="37.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" style="1"/>
+    <col min="5" max="5" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1104,7 +1091,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1114,7 +1101,7 @@
       <c r="C2" s="1">
         <v>1</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="1">
         <v>26.26</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -1124,7 +1111,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -1134,7 +1121,7 @@
       <c r="C3" s="1">
         <v>1</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="1">
         <f>55.6/2</f>
         <v>27.8</v>
       </c>
@@ -1145,7 +1132,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -1165,7 +1152,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>45</v>
       </c>
@@ -1185,7 +1172,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -1205,7 +1192,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -1225,7 +1212,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -1245,7 +1232,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -1265,7 +1252,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>43</v>
       </c>
@@ -1285,7 +1272,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>64</v>
       </c>
@@ -1305,7 +1292,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>75</v>
       </c>
@@ -1315,18 +1302,18 @@
       <c r="C12" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="5">
         <f>4.98/8*6</f>
         <v>3.7350000000000003</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="7" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>76</v>
       </c>
@@ -1336,18 +1323,21 @@
       <c r="C13" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="5">
         <f>9.98*0.6</f>
         <v>5.9880000000000004</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="F13" s="2" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="N13" s="8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>82</v>
       </c>
@@ -1368,7 +1358,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>55</v>
       </c>
@@ -1388,7 +1378,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>69</v>
       </c>
@@ -1398,7 +1388,7 @@
       <c r="C16" s="1">
         <v>1</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="1">
         <v>1.0900000000000001</v>
       </c>
       <c r="E16" s="1" t="s">
@@ -1408,7 +1398,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>68</v>
       </c>
@@ -1418,7 +1408,7 @@
       <c r="C17" s="1">
         <v>1</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="1">
         <v>0.06</v>
       </c>
       <c r="E17" s="1" t="s">
@@ -1428,7 +1418,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>67</v>
       </c>
@@ -1438,7 +1428,7 @@
       <c r="C18" s="1">
         <v>1</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="1">
         <v>0.91</v>
       </c>
       <c r="E18" s="1" t="s">
@@ -1447,8 +1437,11 @@
       <c r="F18" s="3" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="N18" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>74</v>
       </c>
@@ -1458,7 +1451,7 @@
       <c r="C19" s="1">
         <v>4</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="1">
         <v>0.05</v>
       </c>
       <c r="E19" s="1" t="s">
@@ -1468,23 +1461,43 @@
         <v>70</v>
       </c>
     </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="1">
+        <v>3</v>
+      </c>
+      <c r="D20" s="1">
+        <v>6</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="N20" s="8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N21" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N22" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N23" s="8" t="s">
+        <v>88</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="E1:E15 E20:E1048576">
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
-      <formula>"Y"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E16:E17">
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
-      <formula>"Y"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E18">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
-      <formula>"Y"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E19">
+  <conditionalFormatting sqref="E1:E1048576">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Y"</formula>
     </cfRule>
@@ -1506,6 +1519,7 @@
     <hyperlink ref="F9" r:id="rId14" xr:uid="{751BAEB2-26DC-4CAF-8D96-A38FD9446E87}"/>
     <hyperlink ref="F11" r:id="rId15" xr:uid="{9B3802E2-0DAA-4495-8E7B-C8A9F6A2FFA8}"/>
     <hyperlink ref="F19" r:id="rId16" xr:uid="{8B7798E1-B9EF-4C27-8F45-57F8754CF6C6}"/>
+    <hyperlink ref="F12" r:id="rId17" xr:uid="{DAC881B0-F10F-4F69-8986-0AAA523A24EF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1516,18 +1530,18 @@
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" style="1"/>
-    <col min="4" max="4" width="10.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="2"/>
+    <col min="1" max="1" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" style="1"/>
+    <col min="4" max="4" width="10.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1547,7 +1561,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>40</v>
       </c>
@@ -1567,7 +1581,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>66</v>
       </c>
@@ -1577,7 +1591,7 @@
       <c r="C3" s="1">
         <v>2</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="1">
         <v>0.11</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -1587,7 +1601,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -1607,7 +1621,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>57</v>
       </c>
@@ -1627,7 +1641,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -1647,7 +1661,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -1657,7 +1671,7 @@
       <c r="C7" s="1">
         <v>2</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="5">
         <f>11.99/2</f>
         <v>5.9950000000000001</v>
       </c>
@@ -1668,7 +1682,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -1688,7 +1702,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>54</v>
       </c>
@@ -1704,8 +1718,13 @@
       <c r="E9" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="7" t="s">
         <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F10" s="9" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1730,17 +1749,17 @@
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" style="1" customWidth="1"/>
-    <col min="4" max="5" width="12.140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="2"/>
+    <col min="2" max="2" width="11.5546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.88671875" style="1" customWidth="1"/>
+    <col min="4" max="5" width="12.109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1760,7 +1779,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1774,13 +1793,16 @@
         <v>3.64</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="M2" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1799,8 +1821,11 @@
       <c r="F3" s="3" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="M3" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1820,7 +1845,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -1857,11 +1882,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c440327c-db0c-40f7-973b-7bc2ae283ce2" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2090,27 +2116,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c440327c-db0c-40f7-973b-7bc2ae283ce2" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F120B44-02FC-4D2A-B0A5-AADC531A6E78}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{140E0E22-42B5-4B4A-934D-04548B25B00B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="c440327c-db0c-40f7-973b-7bc2ae283ce2"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="3bf09d50-f695-4e18-a2ec-955b0ff6d5dc"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2135,9 +2151,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{140E0E22-42B5-4B4A-934D-04548B25B00B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F120B44-02FC-4D2A-B0A5-AADC531A6E78}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="c440327c-db0c-40f7-973b-7bc2ae283ce2"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="3bf09d50-f695-4e18-a2ec-955b0ff6d5dc"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/CostBreakdown.xlsx
+++ b/CostBreakdown.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jpreisle\Documents\Visual Studio\Git\451-DBF-Team01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jpreisle\Documents\GitHub\451-DBF-Team01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{812E67BB-1D44-4D6D-9542-41B82AC33CDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30CE0B5A-9AC3-48EE-B041-D981C7776F01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="831" activeTab="5" xr2:uid="{C684E4FE-65D8-41BB-8319-3046AEA9131B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="831" activeTab="3" xr2:uid="{C684E4FE-65D8-41BB-8319-3046AEA9131B}"/>
   </bookViews>
   <sheets>
     <sheet name="Aircraft Cost Grand Total" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="97">
   <si>
     <t>M4 30mm bolt</t>
   </si>
@@ -64,12 +64,6 @@
     <t>Link</t>
   </si>
   <si>
-    <t>10x7E Prop</t>
-  </si>
-  <si>
-    <t>Cobra 3520/10</t>
-  </si>
-  <si>
     <t>RC Electric Parts 80A ESC</t>
   </si>
   <si>
@@ -130,9 +124,6 @@
     <t>https://www.homedepot.com/p/Owens-Corning-FOAMULAR-NGX-F-250-2-in-x-4-ft-x-8-ft-SSE-R-10-XPS-Rigid-Foam-Board-Insulation-52DDNGX/315197962</t>
   </si>
   <si>
-    <t>https://www.apcprop.com/product/10x7e/?v=0b3b97fa6688</t>
-  </si>
-  <si>
     <t>Purchased</t>
   </si>
   <si>
@@ -151,9 +142,6 @@
     <t>Propulsion</t>
   </si>
   <si>
-    <t>https://www.cobramotorsusa.com/motors-3520-10.html</t>
-  </si>
-  <si>
     <t>https://www.amazon.com/RC-Electric-Controller-Brushless-Motors/dp/B071GRSFBD?th=1</t>
   </si>
   <si>
@@ -295,21 +283,6 @@
     <t>Aluminum 40mm x 8 mm OD Spacer</t>
   </si>
   <si>
-    <t>3M Pads</t>
-  </si>
-  <si>
-    <t>change to PETG</t>
-  </si>
-  <si>
-    <t>find cost and verify quantity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">single sided velcro </t>
-  </si>
-  <si>
-    <t>Duct Tape</t>
-  </si>
-  <si>
     <t>Bambu Skewers</t>
   </si>
   <si>
@@ -319,10 +292,49 @@
     <t>maybe use easy connectors instead</t>
   </si>
   <si>
-    <t>check 3520/12</t>
-  </si>
-  <si>
-    <t>check 11x8E</t>
+    <t>11x85E Prop</t>
+  </si>
+  <si>
+    <t>Cobra 3520/12</t>
+  </si>
+  <si>
+    <t>https://www.cobramotorsusa.com/motors-3520-12.html</t>
+  </si>
+  <si>
+    <t>https://us.store.bambulab.com/products/petg-basic</t>
+  </si>
+  <si>
+    <t>https://www.horizonhobby.com/product/apc-landing-products-electric-propeller-11-x-8.5e/APC11085E.html</t>
+  </si>
+  <si>
+    <t>https://www.uline.com/Product/Detail/S-24954/3M-Double-Sided-Tape/3M-GPT-020-Double-Coated-Tape-1-2-x-55-yds?pricode=WB2129&amp;gadtype=pla&amp;id=S-24954&amp;ad_group_id=145971513970&amp;gad_source=1&amp;gad_campaignid=11612151501&amp;gbraid=0AAAAAD_uetMWPvmgHv3q_pW1Ap2XPjNcU&amp;gclid=CjwKCAjwxeHWBhBPEiwAiqtQ-fXMrRlgI_ldfpzj6iy0tx9E9ZY5jWXLAkurdtsnGW43uC5BHwLfohoCeCEQAvD_BwE</t>
+  </si>
+  <si>
+    <t>3m double sided tape</t>
+  </si>
+  <si>
+    <t>6 ft</t>
+  </si>
+  <si>
+    <t>adhesive velcro singe sided</t>
+  </si>
+  <si>
+    <t>5 ft</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/94985K27/</t>
+  </si>
+  <si>
+    <t>Duct tape</t>
+  </si>
+  <si>
+    <t>10 ft</t>
+  </si>
+  <si>
+    <t>https://www.homedepot.com/p/Duck-Pro-1-88-in-x-60-yds-Silver-All-Purpose-Duct-Tape-242760/309334754</t>
+  </si>
+  <si>
+    <t>https://www.homedepot.com/p/GrillPro-100-Piece-12-in-Bamboo-Skewers-11070/322906473</t>
   </si>
 </sst>
 </file>
@@ -810,19 +822,19 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="16.5546875" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="4">
         <f>SUM('Per Assembly Cost --&gt;'!B:B)</f>
-        <v>361.51941778975743</v>
+        <v>367.17941778975739</v>
       </c>
     </row>
   </sheetData>
@@ -845,54 +857,54 @@
     <tabColor theme="1"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.33203125" customWidth="1"/>
-    <col min="2" max="2" width="22.88671875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="23.28515625" customWidth="1"/>
+    <col min="2" max="2" width="22.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B2" s="5">
         <f>SUM('Avionics BOM'!D:D)</f>
         <v>14.695417789757411</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B3" s="1">
         <f>SUM('Structures BOM'!D:D)</f>
-        <v>152.80300000000003</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+        <v>157.93299999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B4" s="1">
         <f>SUM('Mechanisms BOM'!D:D)</f>
         <v>53.330999999999996</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B5" s="1">
         <f>SUM('Propulsion BOM'!D:D)</f>
-        <v>140.69</v>
+        <v>141.22</v>
       </c>
     </row>
   </sheetData>
@@ -906,22 +918,22 @@
     <tabColor theme="0"/>
   </sheetPr>
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.33203125" customWidth="1"/>
-    <col min="2" max="2" width="10.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.109375" style="1"/>
-    <col min="4" max="4" width="10.33203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.109375" style="2"/>
+    <col min="1" max="1" width="30.28515625" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="1"/>
+    <col min="4" max="4" width="10.28515625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>3</v>
@@ -930,18 +942,18 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C2" s="1">
         <v>4</v>
@@ -950,18 +962,18 @@
         <v>7.16</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C3" s="1">
         <v>1</v>
@@ -970,18 +982,18 @@
         <v>1.59</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C4" s="1">
         <v>3</v>
@@ -991,18 +1003,18 @@
         <v>2.9699999999999998</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C5" s="1">
         <v>20</v>
@@ -1012,18 +1024,18 @@
         <v>2.6954177897574123</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C6" s="1">
         <v>1</v>
@@ -1032,10 +1044,10 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1061,22 +1073,22 @@
     <tabColor theme="0"/>
   </sheetPr>
   <dimension ref="A1:N23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" style="1"/>
-    <col min="5" max="5" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.109375" style="2"/>
+    <col min="1" max="1" width="37.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="1"/>
+    <col min="5" max="5" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>3</v>
@@ -1085,18 +1097,18 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
@@ -1105,18 +1117,18 @@
         <v>26.26</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C3" s="1">
         <v>1</v>
@@ -1126,18 +1138,18 @@
         <v>27.8</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C4" s="1">
         <v>5</v>
@@ -1146,18 +1158,18 @@
         <v>2.97</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C5" s="1">
         <v>25</v>
@@ -1166,18 +1178,18 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C6" s="1">
         <v>25</v>
@@ -1186,18 +1198,18 @@
         <v>5.55</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C7" s="1">
         <v>100</v>
@@ -1206,18 +1218,18 @@
         <v>3.93</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C8" s="1">
         <v>25</v>
@@ -1226,18 +1238,18 @@
         <v>7.14</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1">
         <v>1</v>
@@ -1246,18 +1258,18 @@
         <v>24.6</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C10" s="1">
         <v>1</v>
@@ -1266,18 +1278,18 @@
         <v>14.27</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>60</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>64</v>
-      </c>
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C11" s="1">
         <v>1</v>
@@ -1286,63 +1298,63 @@
         <v>3.94</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D12" s="5">
         <f>4.98/8*6</f>
         <v>3.7350000000000003</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>72</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="D13" s="5">
         <f>9.98*0.6</f>
         <v>5.9880000000000004</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>75</v>
       </c>
       <c r="N13" s="8" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C14" s="1">
         <v>4</v>
@@ -1352,38 +1364,38 @@
         <v>9.84</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D15" s="1">
         <v>4.07</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C16" s="1">
         <v>1</v>
@@ -1392,18 +1404,18 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C17" s="1">
         <v>1</v>
@@ -1412,41 +1424,39 @@
         <v>0.06</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C18" s="1">
         <v>1</v>
       </c>
       <c r="D18" s="1">
-        <v>0.91</v>
+        <v>0.67</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="N18" s="8" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+      <c r="N18" s="8"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C19" s="1">
         <v>4</v>
@@ -1455,46 +1465,95 @@
         <v>0.05</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C20" s="1">
-        <v>3</v>
+        <v>26</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="D20" s="1">
-        <v>6</v>
+        <v>0.51</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="N20" s="8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="N21" s="8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="N22" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="N23" s="8" t="s">
-        <v>88</v>
-      </c>
+      <c r="N20" s="8"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>90</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D21" s="1">
+        <v>7.76</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="N21" s="8"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>93</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D22" s="1">
+        <v>0.39</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="N22" s="8"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>79</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="1">
+        <v>100</v>
+      </c>
+      <c r="D23" s="1">
+        <v>2.71</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="N23" s="8"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E1:E1048576">
@@ -1520,6 +1579,11 @@
     <hyperlink ref="F11" r:id="rId15" xr:uid="{9B3802E2-0DAA-4495-8E7B-C8A9F6A2FFA8}"/>
     <hyperlink ref="F19" r:id="rId16" xr:uid="{8B7798E1-B9EF-4C27-8F45-57F8754CF6C6}"/>
     <hyperlink ref="F12" r:id="rId17" xr:uid="{DAC881B0-F10F-4F69-8986-0AAA523A24EF}"/>
+    <hyperlink ref="F21" r:id="rId18" xr:uid="{B1936492-E69E-4FC0-9317-A51FD4D180C9}"/>
+    <hyperlink ref="F20" r:id="rId19" display="https://www.uline.com/Product/Detail/S-24954/3M-Double-Sided-Tape/3M-GPT-020-Double-Coated-Tape-1-2-x-55-yds?pricode=WB2129&amp;gadtype=pla&amp;id=S-24954&amp;ad_group_id=145971513970&amp;gad_source=1&amp;gad_campaignid=11612151501&amp;gbraid=0AAAAAD_uetMWPvmgHv3q_pW1Ap2XPjNcU&amp;gclid=CjwKCAjwxeHWBhBPEiwAiqtQ-fXMrRlgI_ldfpzj6iy0tx9E9ZY5jWXLAkurdtsnGW43uC5BHwLfohoCeCEQAvD_BwE" xr:uid="{5269E7F4-3C12-41E9-B94C-7D7110BCCB5B}"/>
+    <hyperlink ref="F13" r:id="rId20" xr:uid="{02A4D3AB-EDC0-4B65-841E-3298AA137928}"/>
+    <hyperlink ref="F22" r:id="rId21" xr:uid="{14143E63-1487-40FC-AEB3-356D1822FE75}"/>
+    <hyperlink ref="F23" r:id="rId22" xr:uid="{B7AFD8AB-FA10-4D01-851E-CFAF953BAB8E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1531,22 +1595,22 @@
     <tabColor theme="0"/>
   </sheetPr>
   <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.88671875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.109375" style="1"/>
-    <col min="4" max="4" width="10.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.109375" style="2"/>
+    <col min="1" max="1" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="1"/>
+    <col min="4" max="4" width="10.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>3</v>
@@ -1555,18 +1619,18 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C2" s="1">
         <v>4</v>
@@ -1575,18 +1639,18 @@
         <v>13.88</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C3" s="1">
         <v>2</v>
@@ -1595,18 +1659,18 @@
         <v>0.11</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C4" s="1">
         <v>4</v>
@@ -1615,18 +1679,18 @@
         <v>2.99</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C5" s="1">
         <v>4</v>
@@ -1635,18 +1699,18 @@
         <v>6.2759999999999998</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C6" s="1">
         <v>1</v>
@@ -1655,18 +1719,18 @@
         <v>14.99</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C7" s="1">
         <v>2</v>
@@ -1676,18 +1740,18 @@
         <v>5.9950000000000001</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C8" s="1">
         <v>1</v>
@@ -1696,18 +1760,18 @@
         <v>8.9700000000000006</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1">
         <v>20</v>
@@ -1716,15 +1780,15 @@
         <v>0.12</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F10" s="9" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1750,21 +1814,21 @@
     <tabColor theme="0"/>
   </sheetPr>
   <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.88671875" style="1" customWidth="1"/>
-    <col min="4" max="5" width="12.109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.109375" style="2"/>
+    <col min="2" max="2" width="11.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" style="1" customWidth="1"/>
+    <col min="4" max="5" width="12.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>3</v>
@@ -1773,41 +1837,39 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
       </c>
       <c r="D2" s="1">
-        <v>3.64</v>
+        <v>4.17</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="M2" s="8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+      <c r="M2" s="8"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C3" s="1">
         <v>1</v>
@@ -1816,21 +1878,19 @@
         <v>57.99</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="M3" s="8" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+      <c r="M3" s="8"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C4" s="1">
         <v>1</v>
@@ -1839,18 +1899,18 @@
         <v>38.49</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C5" s="1">
         <v>1</v>
@@ -1859,10 +1919,10 @@
         <v>40.57</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1882,12 +1942,11 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c440327c-db0c-40f7-973b-7bc2ae283ce2" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2116,17 +2175,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c440327c-db0c-40f7-973b-7bc2ae283ce2" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{140E0E22-42B5-4B4A-934D-04548B25B00B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F120B44-02FC-4D2A-B0A5-AADC531A6E78}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="c440327c-db0c-40f7-973b-7bc2ae283ce2"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="3bf09d50-f695-4e18-a2ec-955b0ff6d5dc"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2151,18 +2220,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F120B44-02FC-4D2A-B0A5-AADC531A6E78}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{140E0E22-42B5-4B4A-934D-04548B25B00B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="c440327c-db0c-40f7-973b-7bc2ae283ce2"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="3bf09d50-f695-4e18-a2ec-955b0ff6d5dc"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/CostBreakdown.xlsx
+++ b/CostBreakdown.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jpreisle\Documents\GitHub\451-DBF-Team01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jpreisle\Documents\Visual Studio\Git\451-DBF-Team01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30CE0B5A-9AC3-48EE-B041-D981C7776F01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EF93C26-873B-4C6A-94E0-5DB7660CE169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="831" activeTab="3" xr2:uid="{C684E4FE-65D8-41BB-8319-3046AEA9131B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="831" activeTab="4" xr2:uid="{C684E4FE-65D8-41BB-8319-3046AEA9131B}"/>
   </bookViews>
   <sheets>
     <sheet name="Aircraft Cost Grand Total" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="103">
   <si>
     <t>M4 30mm bolt</t>
   </si>
@@ -82,9 +82,6 @@
     <t>1/16 x 1/2 x 1/2 aluminum tube - 6ft</t>
   </si>
   <si>
-    <t>Plywood 4x8</t>
-  </si>
-  <si>
     <t xml:space="preserve">Foam Board </t>
   </si>
   <si>
@@ -118,9 +115,6 @@
     <t>https://www.mcmaster.com/products/91290a647/</t>
   </si>
   <si>
-    <t>https://www.homedepot.com/p/Plytanium-1-4-in-x-4-ft-x-8-ft-BC-Sanded-Pine-Plywood-235552/100063669</t>
-  </si>
-  <si>
     <t>https://www.homedepot.com/p/Owens-Corning-FOAMULAR-NGX-F-250-2-in-x-4-ft-x-8-ft-SSE-R-10-XPS-Rigid-Foam-Board-Insulation-52DDNGX/315197962</t>
   </si>
   <si>
@@ -335,6 +329,30 @@
   </si>
   <si>
     <t>https://www.homedepot.com/p/GrillPro-100-Piece-12-in-Bamboo-Skewers-11070/322906473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Birch plywood .205 In </t>
+  </si>
+  <si>
+    <t>2ft x 4ft</t>
+  </si>
+  <si>
+    <t>https://www.homedepot.com/p/SANDEPLY-5-2mm-Sandeply-Plywood-1-4-in-Category-Common-1-4-in-x-4-ft-x-8-ft-Actual-0-205-in-x-48-in-x-96-in-479023/203414042</t>
+  </si>
+  <si>
+    <t>JB WELD</t>
+  </si>
+  <si>
+    <t>1.6 ft</t>
+  </si>
+  <si>
+    <t>1 package</t>
+  </si>
+  <si>
+    <t>aluminum tail tube 1/4 in OD</t>
+  </si>
+  <si>
+    <t>change to 2mm diameter</t>
   </si>
 </sst>
 </file>
@@ -822,19 +840,19 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" customWidth="1"/>
+    <col min="2" max="2" width="16.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="4">
         <f>SUM('Per Assembly Cost --&gt;'!B:B)</f>
-        <v>367.17941778975739</v>
+        <v>348.99941778975739</v>
       </c>
     </row>
   </sheetData>
@@ -857,50 +875,50 @@
     <tabColor theme="1"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.28515625" customWidth="1"/>
-    <col min="2" max="2" width="22.85546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="23.33203125" customWidth="1"/>
+    <col min="2" max="2" width="22.88671875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B2" s="5">
         <f>SUM('Avionics BOM'!D:D)</f>
         <v>14.695417789757411</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B3" s="1">
         <f>SUM('Structures BOM'!D:D)</f>
-        <v>157.93299999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>139.75299999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B4" s="1">
         <f>SUM('Mechanisms BOM'!D:D)</f>
         <v>53.330999999999996</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B5" s="1">
         <f>SUM('Propulsion BOM'!D:D)</f>
@@ -918,17 +936,17 @@
     <tabColor theme="0"/>
   </sheetPr>
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.28515625" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" style="1"/>
-    <col min="4" max="4" width="10.28515625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="2"/>
+    <col min="1" max="1" width="30.33203125" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" style="1"/>
+    <col min="4" max="4" width="10.33203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -942,18 +960,18 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C2" s="1">
         <v>4</v>
@@ -962,18 +980,18 @@
         <v>7.16</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C3" s="1">
         <v>1</v>
@@ -982,18 +1000,18 @@
         <v>1.59</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C4" s="1">
         <v>3</v>
@@ -1003,18 +1021,18 @@
         <v>2.9699999999999998</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C5" s="1">
         <v>20</v>
@@ -1024,18 +1042,18 @@
         <v>2.6954177897574123</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C6" s="1">
         <v>1</v>
@@ -1044,10 +1062,10 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1072,18 +1090,18 @@
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="A1:N23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="1"/>
-    <col min="5" max="5" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="2"/>
+    <col min="1" max="1" width="37.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" style="1"/>
+    <col min="5" max="5" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1097,38 +1115,38 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" s="1">
+        <v>8.08</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="1">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1">
-        <v>26.26</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
       <c r="B3" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C3" s="1">
         <v>1</v>
@@ -1138,18 +1156,18 @@
         <v>27.8</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C4" s="1">
         <v>5</v>
@@ -1158,18 +1176,18 @@
         <v>2.97</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C5" s="1">
         <v>25</v>
@@ -1178,18 +1196,18 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C6" s="1">
         <v>25</v>
@@ -1198,18 +1216,18 @@
         <v>5.55</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C7" s="1">
         <v>100</v>
@@ -1218,18 +1236,18 @@
         <v>3.93</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C8" s="1">
         <v>25</v>
@@ -1238,18 +1256,18 @@
         <v>7.14</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C9" s="1">
         <v>1</v>
@@ -1258,18 +1276,18 @@
         <v>24.6</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C10" s="1">
         <v>1</v>
@@ -1278,18 +1296,18 @@
         <v>14.27</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C11" s="1">
         <v>1</v>
@@ -1298,63 +1316,63 @@
         <v>3.94</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D12" s="5">
         <f>4.98/8*6</f>
         <v>3.7350000000000003</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D13" s="5">
         <f>9.98*0.6</f>
         <v>5.9880000000000004</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="N13" s="8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C14" s="1">
         <v>4</v>
@@ -1364,38 +1382,38 @@
         <v>9.84</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D15" s="1">
         <v>4.07</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C16" s="1">
         <v>1</v>
@@ -1404,18 +1422,18 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C17" s="1">
         <v>1</v>
@@ -1424,18 +1442,18 @@
         <v>0.06</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F17" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>63</v>
-      </c>
       <c r="B18" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C18" s="1">
         <v>1</v>
@@ -1444,19 +1462,19 @@
         <v>0.67</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N18" s="8"/>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C19" s="1">
         <v>4</v>
@@ -1465,81 +1483,81 @@
         <v>0.05</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D20" s="1">
         <v>0.51</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="N20" s="8"/>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D21" s="1">
         <v>7.76</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F21" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="N21" s="8"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>91</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="N21" s="8"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>93</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>94</v>
       </c>
       <c r="D22" s="1">
         <v>0.39</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N22" s="8"/>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C23" s="1">
         <v>100</v>
@@ -1548,12 +1566,40 @@
         <v>2.71</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N23" s="8"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>98</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>101</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>53</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E1:E1048576">
@@ -1570,20 +1616,19 @@
     <hyperlink ref="F14" r:id="rId6" xr:uid="{A91A1DE5-4331-40CB-B90C-715E0BCCB855}"/>
     <hyperlink ref="F15" r:id="rId7" xr:uid="{6293C65C-7FE4-4A84-B068-EDC9724F2BCC}"/>
     <hyperlink ref="F3" r:id="rId8" xr:uid="{EE40E960-AE93-490E-8684-32B42CB94C63}"/>
-    <hyperlink ref="F2" r:id="rId9" xr:uid="{20180B92-8ABC-43AC-BBB8-7C093E6B2F3E}"/>
-    <hyperlink ref="F6" r:id="rId10" xr:uid="{DAE67438-2EA2-46E6-AE59-3CE1BA52DE6A}"/>
-    <hyperlink ref="F4" r:id="rId11" xr:uid="{675196D7-5C58-487C-8B15-98E28F3CC124}"/>
-    <hyperlink ref="F8" r:id="rId12" xr:uid="{77BD64C6-BF95-404A-B01F-81F95BAFFFCD}"/>
-    <hyperlink ref="F7" r:id="rId13" xr:uid="{3C1E28BD-D3E4-46AC-A0D8-E327EE566BE4}"/>
-    <hyperlink ref="F9" r:id="rId14" xr:uid="{751BAEB2-26DC-4CAF-8D96-A38FD9446E87}"/>
-    <hyperlink ref="F11" r:id="rId15" xr:uid="{9B3802E2-0DAA-4495-8E7B-C8A9F6A2FFA8}"/>
-    <hyperlink ref="F19" r:id="rId16" xr:uid="{8B7798E1-B9EF-4C27-8F45-57F8754CF6C6}"/>
-    <hyperlink ref="F12" r:id="rId17" xr:uid="{DAC881B0-F10F-4F69-8986-0AAA523A24EF}"/>
-    <hyperlink ref="F21" r:id="rId18" xr:uid="{B1936492-E69E-4FC0-9317-A51FD4D180C9}"/>
-    <hyperlink ref="F20" r:id="rId19" display="https://www.uline.com/Product/Detail/S-24954/3M-Double-Sided-Tape/3M-GPT-020-Double-Coated-Tape-1-2-x-55-yds?pricode=WB2129&amp;gadtype=pla&amp;id=S-24954&amp;ad_group_id=145971513970&amp;gad_source=1&amp;gad_campaignid=11612151501&amp;gbraid=0AAAAAD_uetMWPvmgHv3q_pW1Ap2XPjNcU&amp;gclid=CjwKCAjwxeHWBhBPEiwAiqtQ-fXMrRlgI_ldfpzj6iy0tx9E9ZY5jWXLAkurdtsnGW43uC5BHwLfohoCeCEQAvD_BwE" xr:uid="{5269E7F4-3C12-41E9-B94C-7D7110BCCB5B}"/>
-    <hyperlink ref="F13" r:id="rId20" xr:uid="{02A4D3AB-EDC0-4B65-841E-3298AA137928}"/>
-    <hyperlink ref="F22" r:id="rId21" xr:uid="{14143E63-1487-40FC-AEB3-356D1822FE75}"/>
-    <hyperlink ref="F23" r:id="rId22" xr:uid="{B7AFD8AB-FA10-4D01-851E-CFAF953BAB8E}"/>
+    <hyperlink ref="F6" r:id="rId9" xr:uid="{DAE67438-2EA2-46E6-AE59-3CE1BA52DE6A}"/>
+    <hyperlink ref="F4" r:id="rId10" xr:uid="{675196D7-5C58-487C-8B15-98E28F3CC124}"/>
+    <hyperlink ref="F8" r:id="rId11" xr:uid="{77BD64C6-BF95-404A-B01F-81F95BAFFFCD}"/>
+    <hyperlink ref="F7" r:id="rId12" xr:uid="{3C1E28BD-D3E4-46AC-A0D8-E327EE566BE4}"/>
+    <hyperlink ref="F9" r:id="rId13" xr:uid="{751BAEB2-26DC-4CAF-8D96-A38FD9446E87}"/>
+    <hyperlink ref="F11" r:id="rId14" xr:uid="{9B3802E2-0DAA-4495-8E7B-C8A9F6A2FFA8}"/>
+    <hyperlink ref="F19" r:id="rId15" xr:uid="{8B7798E1-B9EF-4C27-8F45-57F8754CF6C6}"/>
+    <hyperlink ref="F12" r:id="rId16" xr:uid="{DAC881B0-F10F-4F69-8986-0AAA523A24EF}"/>
+    <hyperlink ref="F21" r:id="rId17" xr:uid="{B1936492-E69E-4FC0-9317-A51FD4D180C9}"/>
+    <hyperlink ref="F20" r:id="rId18" display="https://www.uline.com/Product/Detail/S-24954/3M-Double-Sided-Tape/3M-GPT-020-Double-Coated-Tape-1-2-x-55-yds?pricode=WB2129&amp;gadtype=pla&amp;id=S-24954&amp;ad_group_id=145971513970&amp;gad_source=1&amp;gad_campaignid=11612151501&amp;gbraid=0AAAAAD_uetMWPvmgHv3q_pW1Ap2XPjNcU&amp;gclid=CjwKCAjwxeHWBhBPEiwAiqtQ-fXMrRlgI_ldfpzj6iy0tx9E9ZY5jWXLAkurdtsnGW43uC5BHwLfohoCeCEQAvD_BwE" xr:uid="{5269E7F4-3C12-41E9-B94C-7D7110BCCB5B}"/>
+    <hyperlink ref="F13" r:id="rId19" xr:uid="{02A4D3AB-EDC0-4B65-841E-3298AA137928}"/>
+    <hyperlink ref="F22" r:id="rId20" xr:uid="{14143E63-1487-40FC-AEB3-356D1822FE75}"/>
+    <hyperlink ref="F23" r:id="rId21" xr:uid="{B7AFD8AB-FA10-4D01-851E-CFAF953BAB8E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1594,18 +1639,18 @@
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" style="1"/>
-    <col min="4" max="4" width="10.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="2"/>
+    <col min="1" max="1" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" style="1"/>
+    <col min="4" max="4" width="10.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1619,18 +1664,18 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C2" s="1">
         <v>4</v>
@@ -1639,18 +1684,18 @@
         <v>13.88</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C3" s="1">
         <v>2</v>
@@ -1659,18 +1704,18 @@
         <v>0.11</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C4" s="1">
         <v>4</v>
@@ -1679,18 +1724,18 @@
         <v>2.99</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C5" s="1">
         <v>4</v>
@@ -1699,18 +1744,21 @@
         <v>6.2759999999999998</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C6" s="1">
         <v>1</v>
@@ -1719,18 +1767,18 @@
         <v>14.99</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C7" s="1">
         <v>2</v>
@@ -1740,18 +1788,18 @@
         <v>5.9950000000000001</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C8" s="1">
         <v>1</v>
@@ -1760,18 +1808,18 @@
         <v>8.9700000000000006</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C9" s="1">
         <v>20</v>
@@ -1780,15 +1828,15 @@
         <v>0.12</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F10" s="9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1814,16 +1862,16 @@
     <tabColor theme="0"/>
   </sheetPr>
   <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" style="1" customWidth="1"/>
-    <col min="4" max="5" width="12.140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="2"/>
+    <col min="2" max="2" width="11.5546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.88671875" style="1" customWidth="1"/>
+    <col min="4" max="5" width="12.109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1837,18 +1885,18 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
@@ -1857,19 +1905,19 @@
         <v>4.17</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="M2" s="8"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C3" s="1">
         <v>1</v>
@@ -1878,19 +1926,19 @@
         <v>57.99</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="M3" s="8"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C4" s="1">
         <v>1</v>
@@ -1899,18 +1947,18 @@
         <v>38.49</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C5" s="1">
         <v>1</v>
@@ -1919,10 +1967,10 @@
         <v>40.57</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1942,11 +1990,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c440327c-db0c-40f7-973b-7bc2ae283ce2" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2175,27 +2224,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c440327c-db0c-40f7-973b-7bc2ae283ce2" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F120B44-02FC-4D2A-B0A5-AADC531A6E78}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{140E0E22-42B5-4B4A-934D-04548B25B00B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="c440327c-db0c-40f7-973b-7bc2ae283ce2"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="3bf09d50-f695-4e18-a2ec-955b0ff6d5dc"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2220,9 +2259,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{140E0E22-42B5-4B4A-934D-04548B25B00B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F120B44-02FC-4D2A-B0A5-AADC531A6E78}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="c440327c-db0c-40f7-973b-7bc2ae283ce2"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="3bf09d50-f695-4e18-a2ec-955b0ff6d5dc"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/CostBreakdown.xlsx
+++ b/CostBreakdown.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jpreisle\Documents\Visual Studio\Git\451-DBF-Team01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jpreisle\Documents\GitHub\451-DBF-Team01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EF93C26-873B-4C6A-94E0-5DB7660CE169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E25B8A8D-422B-4FE0-A8C2-9CE3BC6F0834}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="831" activeTab="4" xr2:uid="{C684E4FE-65D8-41BB-8319-3046AEA9131B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="831" activeTab="4" xr2:uid="{C684E4FE-65D8-41BB-8319-3046AEA9131B}"/>
   </bookViews>
   <sheets>
     <sheet name="Aircraft Cost Grand Total" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="106">
   <si>
     <t>M4 30mm bolt</t>
   </si>
@@ -286,9 +286,6 @@
     <t>maybe use easy connectors instead</t>
   </si>
   <si>
-    <t>11x85E Prop</t>
-  </si>
-  <si>
     <t>Cobra 3520/12</t>
   </si>
   <si>
@@ -298,9 +295,6 @@
     <t>https://us.store.bambulab.com/products/petg-basic</t>
   </si>
   <si>
-    <t>https://www.horizonhobby.com/product/apc-landing-products-electric-propeller-11-x-8.5e/APC11085E.html</t>
-  </si>
-  <si>
     <t>https://www.uline.com/Product/Detail/S-24954/3M-Double-Sided-Tape/3M-GPT-020-Double-Coated-Tape-1-2-x-55-yds?pricode=WB2129&amp;gadtype=pla&amp;id=S-24954&amp;ad_group_id=145971513970&amp;gad_source=1&amp;gad_campaignid=11612151501&amp;gbraid=0AAAAAD_uetMWPvmgHv3q_pW1Ap2XPjNcU&amp;gclid=CjwKCAjwxeHWBhBPEiwAiqtQ-fXMrRlgI_ldfpzj6iy0tx9E9ZY5jWXLAkurdtsnGW43uC5BHwLfohoCeCEQAvD_BwE</t>
   </si>
   <si>
@@ -353,6 +347,21 @@
   </si>
   <si>
     <t>change to 2mm diameter</t>
+  </si>
+  <si>
+    <t>11x8E Prop</t>
+  </si>
+  <si>
+    <t>https://www.horizonhobby.com/product/apc-landing-products-electric-propeller-11-x-8e/APC11080E.html</t>
+  </si>
+  <si>
+    <t>https://www.homedepot.com/p/J-B-Weld-Two-1-oz-Twin-Tube-Cold-Weld-Epoxy-8265-s/100189012</t>
+  </si>
+  <si>
+    <t>cant find cheap version</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/8978K205-8978K912/</t>
   </si>
 </sst>
 </file>
@@ -840,19 +849,19 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="16.5546875" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="4">
         <f>SUM('Per Assembly Cost --&gt;'!B:B)</f>
-        <v>348.99941778975739</v>
+        <v>355.97941778975735</v>
       </c>
     </row>
   </sheetData>
@@ -875,13 +884,13 @@
     <tabColor theme="1"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.33203125" customWidth="1"/>
-    <col min="2" max="2" width="22.88671875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="23.28515625" customWidth="1"/>
+    <col min="2" max="2" width="22.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
@@ -889,7 +898,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -898,16 +907,16 @@
         <v>14.695417789757411</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>27</v>
       </c>
       <c r="B3" s="1">
         <f>SUM('Structures BOM'!D:D)</f>
-        <v>139.75299999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+        <v>146.73299999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -916,7 +925,7 @@
         <v>53.330999999999996</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>29</v>
       </c>
@@ -936,17 +945,17 @@
     <tabColor theme="0"/>
   </sheetPr>
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.33203125" customWidth="1"/>
-    <col min="2" max="2" width="10.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.109375" style="1"/>
-    <col min="4" max="4" width="10.33203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.109375" style="2"/>
+    <col min="1" max="1" width="30.28515625" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="1"/>
+    <col min="4" max="4" width="10.28515625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -966,7 +975,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>42</v>
       </c>
@@ -986,7 +995,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>44</v>
       </c>
@@ -1006,7 +1015,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -1027,7 +1036,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -1048,7 +1057,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>65</v>
       </c>
@@ -1091,17 +1100,17 @@
     <tabColor theme="0"/>
   </sheetPr>
   <dimension ref="A1:N25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" style="1"/>
-    <col min="5" max="5" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.109375" style="2"/>
+    <col min="1" max="1" width="37.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="1"/>
+    <col min="5" max="5" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1121,15 +1130,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D2" s="1">
         <v>8.08</v>
@@ -1138,10 +1147,10 @@
         <v>53</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1162,7 +1171,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -1182,7 +1191,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>39</v>
       </c>
@@ -1202,7 +1211,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -1222,7 +1231,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1242,7 +1251,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1262,7 +1271,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -1282,7 +1291,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -1302,7 +1311,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>58</v>
       </c>
@@ -1322,7 +1331,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>69</v>
       </c>
@@ -1343,7 +1352,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>70</v>
       </c>
@@ -1367,7 +1376,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>76</v>
       </c>
@@ -1388,7 +1397,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>49</v>
       </c>
@@ -1408,7 +1417,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>63</v>
       </c>
@@ -1428,7 +1437,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>62</v>
       </c>
@@ -1448,7 +1457,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>61</v>
       </c>
@@ -1465,11 +1474,11 @@
         <v>35</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N18" s="8"/>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>68</v>
       </c>
@@ -1489,15 +1498,15 @@
         <v>64</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D20" s="1">
         <v>0.51</v>
@@ -1506,19 +1515,19 @@
         <v>53</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N20" s="8"/>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D21" s="1">
         <v>7.76</v>
@@ -1527,19 +1536,19 @@
         <v>54</v>
       </c>
       <c r="F21" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="N21" s="8"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>89</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="N21" s="8"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>91</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>92</v>
       </c>
       <c r="D22" s="1">
         <v>0.39</v>
@@ -1548,11 +1557,11 @@
         <v>53</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N22" s="8"/>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>77</v>
       </c>
@@ -1569,36 +1578,48 @@
         <v>54</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="N23" s="8"/>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>96</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>100</v>
+      <c r="D24" s="1">
+        <v>6.98</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="F24" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>53</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -1629,8 +1650,11 @@
     <hyperlink ref="F13" r:id="rId19" xr:uid="{02A4D3AB-EDC0-4B65-841E-3298AA137928}"/>
     <hyperlink ref="F22" r:id="rId20" xr:uid="{14143E63-1487-40FC-AEB3-356D1822FE75}"/>
     <hyperlink ref="F23" r:id="rId21" xr:uid="{B7AFD8AB-FA10-4D01-851E-CFAF953BAB8E}"/>
+    <hyperlink ref="F25" r:id="rId22" xr:uid="{220600F5-F3D8-4713-9FCF-D0034B1ED51A}"/>
+    <hyperlink ref="F24" r:id="rId23" xr:uid="{25340820-4495-4BA4-8066-28EF3BFF3F70}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId24"/>
 </worksheet>
 </file>
 
@@ -1640,17 +1664,17 @@
     <tabColor theme="0"/>
   </sheetPr>
   <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.88671875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.109375" style="1"/>
-    <col min="4" max="4" width="10.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.109375" style="2"/>
+    <col min="1" max="1" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="1"/>
+    <col min="4" max="4" width="10.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1670,7 +1694,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>34</v>
       </c>
@@ -1690,7 +1714,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>60</v>
       </c>
@@ -1710,7 +1734,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1730,7 +1754,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>51</v>
       </c>
@@ -1750,10 +1774,10 @@
         <v>56</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1773,7 +1797,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -1794,7 +1818,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -1814,7 +1838,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>48</v>
       </c>
@@ -1834,7 +1858,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="F10" s="9" t="s">
         <v>79</v>
       </c>
@@ -1862,16 +1886,16 @@
     <tabColor theme="0"/>
   </sheetPr>
   <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.88671875" style="1" customWidth="1"/>
-    <col min="4" max="5" width="12.109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.109375" style="2"/>
+    <col min="2" max="2" width="11.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" style="1" customWidth="1"/>
+    <col min="4" max="5" width="12.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1891,9 +1915,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>24</v>
@@ -1908,13 +1932,13 @@
         <v>54</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="M2" s="8"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>24</v>
@@ -1929,11 +1953,11 @@
         <v>53</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M3" s="8"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1953,7 +1977,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1980,10 +2004,9 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{F52A4918-E897-4C4E-897E-D5215E045CA6}"/>
-    <hyperlink ref="F3" r:id="rId2" xr:uid="{33A92E14-CC68-4656-B82C-8BE565F4FCFD}"/>
-    <hyperlink ref="F4" r:id="rId3" xr:uid="{50C17E5A-DE64-49D2-A6A1-C7139C62E0DA}"/>
-    <hyperlink ref="F5" r:id="rId4" xr:uid="{B212F068-A19C-47FA-90E5-D3A0FCB21397}"/>
+    <hyperlink ref="F3" r:id="rId1" xr:uid="{33A92E14-CC68-4656-B82C-8BE565F4FCFD}"/>
+    <hyperlink ref="F4" r:id="rId2" xr:uid="{50C17E5A-DE64-49D2-A6A1-C7139C62E0DA}"/>
+    <hyperlink ref="F5" r:id="rId3" xr:uid="{B212F068-A19C-47FA-90E5-D3A0FCB21397}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1999,6 +2022,14 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c440327c-db0c-40f7-973b-7bc2ae283ce2" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006F9431A864773547893222757859AEDB" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8d93b3794edbd64c1f12ce1859fb2ebb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c440327c-db0c-40f7-973b-7bc2ae283ce2" xmlns:ns4="3bf09d50-f695-4e18-a2ec-955b0ff6d5dc" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ab198344f7607dd971ab6c53863418c3" ns3:_="" ns4:_="">
     <xsd:import namespace="c440327c-db0c-40f7-973b-7bc2ae283ce2"/>
@@ -2223,14 +2254,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c440327c-db0c-40f7-973b-7bc2ae283ce2" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{140E0E22-42B5-4B4A-934D-04548B25B00B}">
   <ds:schemaRefs>
@@ -2240,6 +2263,23 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F120B44-02FC-4D2A-B0A5-AADC531A6E78}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="c440327c-db0c-40f7-973b-7bc2ae283ce2"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="3bf09d50-f695-4e18-a2ec-955b0ff6d5dc"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92C5615A-B0FE-40B8-955A-C3851BD0A604}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2256,21 +2296,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F120B44-02FC-4D2A-B0A5-AADC531A6E78}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="c440327c-db0c-40f7-973b-7bc2ae283ce2"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="3bf09d50-f695-4e18-a2ec-955b0ff6d5dc"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/CostBreakdown.xlsx
+++ b/CostBreakdown.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jpreisle\Documents\GitHub\451-DBF-Team01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E25B8A8D-422B-4FE0-A8C2-9CE3BC6F0834}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F880F12-95E5-47CE-B65A-FF4CCACB66C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="831" activeTab="4" xr2:uid="{C684E4FE-65D8-41BB-8319-3046AEA9131B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="831" activeTab="5" xr2:uid="{C684E4FE-65D8-41BB-8319-3046AEA9131B}"/>
   </bookViews>
   <sheets>
     <sheet name="Aircraft Cost Grand Total" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="104">
   <si>
     <t>M4 30mm bolt</t>
   </si>
@@ -280,9 +280,6 @@
     <t>Bambu Skewers</t>
   </si>
   <si>
-    <t>check If we can use this glue</t>
-  </si>
-  <si>
     <t>maybe use easy connectors instead</t>
   </si>
   <si>
@@ -337,31 +334,28 @@
     <t>JB WELD</t>
   </si>
   <si>
-    <t>1.6 ft</t>
-  </si>
-  <si>
     <t>1 package</t>
   </si>
   <si>
-    <t>aluminum tail tube 1/4 in OD</t>
-  </si>
-  <si>
     <t>change to 2mm diameter</t>
   </si>
   <si>
-    <t>11x8E Prop</t>
-  </si>
-  <si>
-    <t>https://www.horizonhobby.com/product/apc-landing-products-electric-propeller-11-x-8e/APC11080E.html</t>
-  </si>
-  <si>
     <t>https://www.homedepot.com/p/J-B-Weld-Two-1-oz-Twin-Tube-Cold-Weld-Epoxy-8265-s/100189012</t>
   </si>
   <si>
-    <t>cant find cheap version</t>
-  </si>
-  <si>
-    <t>https://www.mcmaster.com/8978K205-8978K912/</t>
+    <t>aluminum square tubing 1/4 1/16 wall t</t>
+  </si>
+  <si>
+    <t>3 ft</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/6546K46/</t>
+  </si>
+  <si>
+    <t>https://www.horizonhobby.com/product/apc-landing-products-electric-propeller-11-x-7e/APC11070E.html</t>
+  </si>
+  <si>
+    <t>11x7E Prop</t>
   </si>
 </sst>
 </file>
@@ -861,7 +855,7 @@
       </c>
       <c r="B1" s="4">
         <f>SUM('Per Assembly Cost --&gt;'!B:B)</f>
-        <v>355.97941778975735</v>
+        <v>363.55941778975739</v>
       </c>
     </row>
   </sheetData>
@@ -913,7 +907,7 @@
       </c>
       <c r="B3" s="1">
         <f>SUM('Structures BOM'!D:D)</f>
-        <v>146.73299999999998</v>
+        <v>154.31299999999999</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1132,13 +1126,13 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>94</v>
       </c>
       <c r="D2" s="1">
         <v>8.08</v>
@@ -1147,7 +1141,7 @@
         <v>53</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -1372,9 +1366,7 @@
       <c r="F13" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="N13" s="8" t="s">
-        <v>78</v>
-      </c>
+      <c r="N13" s="8"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -1474,7 +1466,7 @@
         <v>35</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N18" s="8"/>
     </row>
@@ -1500,13 +1492,13 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="D20" s="1">
         <v>0.51</v>
@@ -1515,19 +1507,19 @@
         <v>53</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N20" s="8"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>85</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>87</v>
       </c>
       <c r="D21" s="1">
         <v>7.76</v>
@@ -1536,19 +1528,19 @@
         <v>54</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="N21" s="8"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>90</v>
       </c>
       <c r="D22" s="1">
         <v>0.39</v>
@@ -1557,7 +1549,7 @@
         <v>53</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N22" s="8"/>
     </row>
@@ -1578,19 +1570,19 @@
         <v>54</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N23" s="8"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>95</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="D24" s="1">
         <v>6.98</v>
@@ -1599,7 +1591,7 @@
         <v>53</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
@@ -1610,17 +1602,18 @@
         <v>24</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
+      </c>
+      <c r="D25" s="1">
+        <v>7.58</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>104</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="I25" s="8"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E1:E1048576">
@@ -1774,7 +1767,7 @@
         <v>56</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -1860,7 +1853,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="F10" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -1917,7 +1910,7 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>24</v>
@@ -1938,7 +1931,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>24</v>
@@ -1953,7 +1946,7 @@
         <v>53</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M3" s="8"/>
     </row>
@@ -2007,29 +2000,13 @@
     <hyperlink ref="F3" r:id="rId1" xr:uid="{33A92E14-CC68-4656-B82C-8BE565F4FCFD}"/>
     <hyperlink ref="F4" r:id="rId2" xr:uid="{50C17E5A-DE64-49D2-A6A1-C7139C62E0DA}"/>
     <hyperlink ref="F5" r:id="rId3" xr:uid="{B212F068-A19C-47FA-90E5-D3A0FCB21397}"/>
+    <hyperlink ref="F2" r:id="rId4" xr:uid="{8D12B446-A1E6-4BA4-B34B-90C2C49FCAC1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c440327c-db0c-40f7-973b-7bc2ae283ce2" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006F9431A864773547893222757859AEDB" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8d93b3794edbd64c1f12ce1859fb2ebb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c440327c-db0c-40f7-973b-7bc2ae283ce2" xmlns:ns4="3bf09d50-f695-4e18-a2ec-955b0ff6d5dc" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ab198344f7607dd971ab6c53863418c3" ns3:_="" ns4:_="">
     <xsd:import namespace="c440327c-db0c-40f7-973b-7bc2ae283ce2"/>
@@ -2254,10 +2231,38 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c440327c-db0c-40f7-973b-7bc2ae283ce2" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{140E0E22-42B5-4B4A-934D-04548B25B00B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92C5615A-B0FE-40B8-955A-C3851BD0A604}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="c440327c-db0c-40f7-973b-7bc2ae283ce2"/>
+    <ds:schemaRef ds:uri="3bf09d50-f695-4e18-a2ec-955b0ff6d5dc"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2280,20 +2285,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92C5615A-B0FE-40B8-955A-C3851BD0A604}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{140E0E22-42B5-4B4A-934D-04548B25B00B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="c440327c-db0c-40f7-973b-7bc2ae283ce2"/>
-    <ds:schemaRef ds:uri="3bf09d50-f695-4e18-a2ec-955b0ff6d5dc"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/CostBreakdown.xlsx
+++ b/CostBreakdown.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jpreisle\Documents\GitHub\451-DBF-Team01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F880F12-95E5-47CE-B65A-FF4CCACB66C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3CD51C9-3BB4-4D65-878E-20D4A3DBCD29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="831" activeTab="5" xr2:uid="{C684E4FE-65D8-41BB-8319-3046AEA9131B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="831" activeTab="3" xr2:uid="{C684E4FE-65D8-41BB-8319-3046AEA9131B}"/>
   </bookViews>
   <sheets>
     <sheet name="Aircraft Cost Grand Total" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="104">
   <si>
     <t>M4 30mm bolt</t>
   </si>
@@ -82,9 +82,6 @@
     <t>1/16 x 1/2 x 1/2 aluminum tube - 6ft</t>
   </si>
   <si>
-    <t xml:space="preserve">Foam Board </t>
-  </si>
-  <si>
     <t>Control Horns</t>
   </si>
   <si>
@@ -214,9 +211,6 @@
     <t>https://www.amazon.com/Standard-Control-17-5x26-Airplane-Replacement/dp/B019I0U8NG</t>
   </si>
   <si>
-    <t>https://www.amazon.com/uxcell-1-2mm-450mm-Airplane-Replacement/dp/B08K7SFD44/ref=sr_1_5?dib=eyJ2IjoiMSJ9.Xv4Fl3SO-hjoYWOD4Yyq8eCHEQX1GgJdtS7lgvoIz4I4gE9OJmv0Pfpo33JR1AmjuBR1lGVoHsZTS9NA2lB3Db4m8RU_RmouEuuf60fKcDtOCAsT16KfdGIvOWhHHp3vpcK78yX_YpiwUrBfH_uBmARbqz2aTljlkTVo9tz1jM23THeEwLyOJEs9Ox2Oh3rqOMy85hEGvplJPE06rhEegLODbrXBsUrGEKSKdHLd-WQ.E_9_LKhsTYuPwrU52Ke5dijHkXW8E0HgM0qeneplYhY&amp;dib_tag=se&amp;keywords=control%2Brods&amp;qid=1760542926&amp;sr=8-5&amp;th=1hjoYWOD4Yyq8eCHEQX1GgJdtS7lgvoIz4I4gE9OJmv0Pfpo33JR1AmjuBR1lGVoHsZTS9NA2lB3Db4m8RU_RmouEuuf60fKcDtOCAsT16KfdGIvOWhHHp3vpcK78yX_YpiwUrBfH_uBmARbqz2aTljlkTVo9tz1jM23THeEwLyOJEs9Ox2Oh3rqOMy85hEGvplJPE06rhEegLODbrXBsUrGEKSKdHLd-WQ.E_9_LKhsTYuPwrU52Ke5dijHkXW8E0HgM0qeneplYhY&amp;dib_tag=se&amp;keywords=control%2Brods&amp;qid=1760542926&amp;sr=8-5&amp;th=1</t>
-  </si>
-  <si>
     <t>https://www.horizonhobby.com/product/main-landing-gear-valiant-10cc/HAN508010.html</t>
   </si>
   <si>
@@ -280,9 +274,6 @@
     <t>Bambu Skewers</t>
   </si>
   <si>
-    <t>maybe use easy connectors instead</t>
-  </si>
-  <si>
     <t>Cobra 3520/12</t>
   </si>
   <si>
@@ -334,28 +325,37 @@
     <t>JB WELD</t>
   </si>
   <si>
-    <t>1 package</t>
-  </si>
-  <si>
-    <t>change to 2mm diameter</t>
-  </si>
-  <si>
     <t>https://www.homedepot.com/p/J-B-Weld-Two-1-oz-Twin-Tube-Cold-Weld-Epoxy-8265-s/100189012</t>
   </si>
   <si>
-    <t>aluminum square tubing 1/4 1/16 wall t</t>
-  </si>
-  <si>
-    <t>3 ft</t>
-  </si>
-  <si>
-    <t>https://www.mcmaster.com/6546K46/</t>
-  </si>
-  <si>
     <t>https://www.horizonhobby.com/product/apc-landing-products-electric-propeller-11-x-7e/APC11070E.html</t>
   </si>
   <si>
     <t>11x7E Prop</t>
+  </si>
+  <si>
+    <t>m2 servo screws</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/2153T83/</t>
+  </si>
+  <si>
+    <t>carbon fiber tail tube</t>
+  </si>
+  <si>
+    <t>39 in</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/uxcell-Stainless-Crafts-Helicopter-Airplane/dp/B0F9FLP8ZX/ref=sr_1_1_sspa?crid=34B8IE94O70HA&amp;dib=eyJ2IjoiMSJ9.cU7lrr51XJ6qmYJOtUckRNTVaDGZtMfpKsb4a1nnoWj_3mOwmRlwX9K110lpATxnRlj8VJAXT0BzvVN4j66zfWec5g2koLZJikNByrNtigidG0j0aomu5dc6oTT4FSrP6QrbriTjrcd4Sniqtx8jaakzQk0pkfL_5sQx-lfLcv_kOWs8mObVOVKBTt2oJkXN8LWZhnXeWwgc5mSLuX2crPxBPMxIA-lzOSfG6GJ7Wp0.ZYBiy1ApnXie17T9Ypp93rQ6LX8hMn0YDRb8uOdDDxM&amp;dib_tag=se&amp;keywords=2mm+control+rod+steel&amp;qid=1792720495&amp;sprefix=2mm+control+rod+ste%2Caps%2C263&amp;sr=8-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/92095A457/</t>
+  </si>
+  <si>
+    <t>1/2 package</t>
+  </si>
+  <si>
+    <t>Foam Board 1.5 x 8 ft</t>
   </si>
 </sst>
 </file>
@@ -855,7 +855,7 @@
       </c>
       <c r="B1" s="4">
         <f>SUM('Per Assembly Cost --&gt;'!B:B)</f>
-        <v>363.55941778975739</v>
+        <v>379.55141778975741</v>
       </c>
     </row>
   </sheetData>
@@ -886,7 +886,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
@@ -894,7 +894,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" s="5">
         <f>SUM('Avionics BOM'!D:D)</f>
@@ -903,25 +903,25 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" s="1">
         <f>SUM('Structures BOM'!D:D)</f>
-        <v>154.31299999999999</v>
+        <v>163.273</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" s="1">
         <f>SUM('Mechanisms BOM'!D:D)</f>
-        <v>53.330999999999996</v>
+        <v>60.363</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" s="1">
         <f>SUM('Propulsion BOM'!D:D)</f>
@@ -963,7 +963,7 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C2" s="1">
         <v>4</v>
@@ -983,18 +983,18 @@
         <v>7.16</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C3" s="1">
         <v>1</v>
@@ -1003,18 +1003,18 @@
         <v>1.59</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" s="1">
         <v>3</v>
@@ -1024,18 +1024,18 @@
         <v>2.9699999999999998</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" s="1">
         <v>20</v>
@@ -1045,18 +1045,18 @@
         <v>2.6954177897574123</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C6" s="1">
         <v>1</v>
@@ -1065,10 +1065,10 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1118,7 +1118,7 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
@@ -1126,43 +1126,43 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D2" s="1">
         <v>8.08</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>103</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C3" s="1">
         <v>1</v>
       </c>
       <c r="D3" s="1">
-        <f>55.6/2</f>
-        <v>27.8</v>
+        <f>55.6/2*0.75</f>
+        <v>20.85</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -1170,7 +1170,7 @@
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" s="1">
         <v>5</v>
@@ -1179,18 +1179,18 @@
         <v>2.97</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" s="1">
         <v>25</v>
@@ -1199,10 +1199,10 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -1210,7 +1210,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" s="1">
         <v>25</v>
@@ -1219,10 +1219,10 @@
         <v>5.55</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -1230,7 +1230,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C7" s="1">
         <v>100</v>
@@ -1239,10 +1239,10 @@
         <v>3.93</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -1250,7 +1250,7 @@
         <v>9</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C8" s="1">
         <v>25</v>
@@ -1259,10 +1259,10 @@
         <v>7.14</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -1270,7 +1270,7 @@
         <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C9" s="1">
         <v>1</v>
@@ -1279,18 +1279,18 @@
         <v>24.6</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C10" s="1">
         <v>1</v>
@@ -1299,18 +1299,18 @@
         <v>14.27</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C11" s="1">
         <v>1</v>
@@ -1319,61 +1319,61 @@
         <v>3.94</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D12" s="5">
         <f>4.98/8*6</f>
         <v>3.7350000000000003</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D13" s="5">
         <f>9.98*0.6</f>
         <v>5.9880000000000004</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="N13" s="8"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C14" s="1">
         <v>4</v>
@@ -1383,38 +1383,38 @@
         <v>9.84</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D15" s="1">
         <v>4.07</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C16" s="1">
         <v>1</v>
@@ -1423,18 +1423,18 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C17" s="1">
         <v>1</v>
@@ -1443,18 +1443,18 @@
         <v>0.06</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C18" s="1">
         <v>1</v>
@@ -1463,19 +1463,19 @@
         <v>0.67</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="N18" s="8"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C19" s="1">
         <v>4</v>
@@ -1484,81 +1484,81 @@
         <v>0.05</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D20" s="1">
         <v>0.51</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="N20" s="8"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D21" s="1">
         <v>7.76</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="N21" s="8"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D22" s="1">
         <v>0.39</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="N22" s="8"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C23" s="1">
         <v>100</v>
@@ -1567,51 +1567,52 @@
         <v>2.71</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="N23" s="8"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="D24" s="1">
-        <v>6.98</v>
+        <f>6.98/2</f>
+        <v>3.49</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>98</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>100</v>
-      </c>
       <c r="D25" s="1">
-        <v>7.58</v>
+        <v>26.98</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I25" s="8"/>
     </row>
@@ -1656,7 +1657,7 @@
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.7109375" bestFit="1" customWidth="1"/>
@@ -1681,7 +1682,7 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
@@ -1689,10 +1690,10 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C2" s="1">
         <v>4</v>
@@ -1701,18 +1702,18 @@
         <v>13.88</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C3" s="1">
         <v>2</v>
@@ -1721,18 +1722,18 @@
         <v>0.11</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" s="1">
         <v>4</v>
@@ -1741,41 +1742,40 @@
         <v>2.99</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" s="1">
         <v>4</v>
       </c>
-      <c r="D5" s="1">
-        <v>6.2759999999999998</v>
+      <c r="D5" s="5">
+        <f>22.22/10*4</f>
+        <v>8.8879999999999999</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="M5" s="8" t="s">
-        <v>97</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="M5" s="8"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" s="1">
         <v>1</v>
@@ -1784,18 +1784,18 @@
         <v>14.99</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C7" s="1">
         <v>2</v>
@@ -1805,18 +1805,18 @@
         <v>5.9950000000000001</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C8" s="1">
         <v>1</v>
@@ -1825,18 +1825,18 @@
         <v>8.9700000000000006</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C9" s="1">
         <v>20</v>
@@ -1845,16 +1845,34 @@
         <v>0.12</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="1">
+        <v>25</v>
+      </c>
+      <c r="D10" s="1">
+        <v>4.42</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F9" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="F10" s="9" t="s">
-        <v>78</v>
-      </c>
+      <c r="F10" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="F11" s="9"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E1:E1048576">
@@ -1902,7 +1920,7 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
@@ -1910,10 +1928,10 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
@@ -1922,19 +1940,19 @@
         <v>4.17</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="M2" s="8"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C3" s="1">
         <v>1</v>
@@ -1943,10 +1961,10 @@
         <v>57.99</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="M3" s="8"/>
     </row>
@@ -1955,7 +1973,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" s="1">
         <v>1</v>
@@ -1964,10 +1982,10 @@
         <v>38.49</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -1975,7 +1993,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" s="1">
         <v>1</v>
@@ -1984,10 +2002,10 @@
         <v>40.57</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -2007,6 +2025,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c440327c-db0c-40f7-973b-7bc2ae283ce2" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006F9431A864773547893222757859AEDB" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8d93b3794edbd64c1f12ce1859fb2ebb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c440327c-db0c-40f7-973b-7bc2ae283ce2" xmlns:ns4="3bf09d50-f695-4e18-a2ec-955b0ff6d5dc" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ab198344f7607dd971ab6c53863418c3" ns3:_="" ns4:_="">
     <xsd:import namespace="c440327c-db0c-40f7-973b-7bc2ae283ce2"/>
@@ -2231,38 +2266,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c440327c-db0c-40f7-973b-7bc2ae283ce2" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92C5615A-B0FE-40B8-955A-C3851BD0A604}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{140E0E22-42B5-4B4A-934D-04548B25B00B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="c440327c-db0c-40f7-973b-7bc2ae283ce2"/>
-    <ds:schemaRef ds:uri="3bf09d50-f695-4e18-a2ec-955b0ff6d5dc"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2285,9 +2292,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{140E0E22-42B5-4B4A-934D-04548B25B00B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92C5615A-B0FE-40B8-955A-C3851BD0A604}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="c440327c-db0c-40f7-973b-7bc2ae283ce2"/>
+    <ds:schemaRef ds:uri="3bf09d50-f695-4e18-a2ec-955b0ff6d5dc"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/CostBreakdown.xlsx
+++ b/CostBreakdown.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jpreisle\Documents\GitHub\451-DBF-Team01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3CD51C9-3BB4-4D65-878E-20D4A3DBCD29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85FEECA0-14C6-48F5-A7A4-427EA9E85899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="831" activeTab="3" xr2:uid="{C684E4FE-65D8-41BB-8319-3046AEA9131B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="831" activeTab="4" xr2:uid="{C684E4FE-65D8-41BB-8319-3046AEA9131B}"/>
   </bookViews>
   <sheets>
     <sheet name="Aircraft Cost Grand Total" sheetId="1" r:id="rId1"/>
@@ -855,7 +855,7 @@
       </c>
       <c r="B1" s="4">
         <f>SUM('Per Assembly Cost --&gt;'!B:B)</f>
-        <v>379.55141778975741</v>
+        <v>375.10741778975739</v>
       </c>
     </row>
   </sheetData>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" s="1">
         <f>SUM('Mechanisms BOM'!D:D)</f>
-        <v>60.363</v>
+        <v>55.918999999999997</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1756,11 +1756,11 @@
         <v>23</v>
       </c>
       <c r="C5" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D5" s="5">
-        <f>22.22/10*4</f>
-        <v>8.8879999999999999</v>
+        <f>22.22/10*2</f>
+        <v>4.444</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>52</v>
@@ -2025,23 +2025,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c440327c-db0c-40f7-973b-7bc2ae283ce2" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006F9431A864773547893222757859AEDB" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8d93b3794edbd64c1f12ce1859fb2ebb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c440327c-db0c-40f7-973b-7bc2ae283ce2" xmlns:ns4="3bf09d50-f695-4e18-a2ec-955b0ff6d5dc" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ab198344f7607dd971ab6c53863418c3" ns3:_="" ns4:_="">
     <xsd:import namespace="c440327c-db0c-40f7-973b-7bc2ae283ce2"/>
@@ -2266,10 +2249,38 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c440327c-db0c-40f7-973b-7bc2ae283ce2" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{140E0E22-42B5-4B4A-934D-04548B25B00B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92C5615A-B0FE-40B8-955A-C3851BD0A604}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="c440327c-db0c-40f7-973b-7bc2ae283ce2"/>
+    <ds:schemaRef ds:uri="3bf09d50-f695-4e18-a2ec-955b0ff6d5dc"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2292,20 +2303,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92C5615A-B0FE-40B8-955A-C3851BD0A604}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{140E0E22-42B5-4B4A-934D-04548B25B00B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="c440327c-db0c-40f7-973b-7bc2ae283ce2"/>
-    <ds:schemaRef ds:uri="3bf09d50-f695-4e18-a2ec-955b0ff6d5dc"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/CostBreakdown.xlsx
+++ b/CostBreakdown.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jpreisle\Documents\GitHub\451-DBF-Team01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85FEECA0-14C6-48F5-A7A4-427EA9E85899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CB74598-2BA3-4CF1-BEE9-BC6238BC5F7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="831" activeTab="4" xr2:uid="{C684E4FE-65D8-41BB-8319-3046AEA9131B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="831" activeTab="5" xr2:uid="{C684E4FE-65D8-41BB-8319-3046AEA9131B}"/>
   </bookViews>
   <sheets>
     <sheet name="Aircraft Cost Grand Total" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="105">
   <si>
     <t>M4 30mm bolt</t>
   </si>
@@ -337,12 +337,6 @@
     <t>m2 servo screws</t>
   </si>
   <si>
-    <t>https://www.mcmaster.com/2153T83/</t>
-  </si>
-  <si>
-    <t>carbon fiber tail tube</t>
-  </si>
-  <si>
     <t>39 in</t>
   </si>
   <si>
@@ -355,7 +349,16 @@
     <t>1/2 package</t>
   </si>
   <si>
-    <t>Foam Board 1.5 x 8 ft</t>
+    <t>carbon fiber tail tube .314 in OD</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/2153T84/</t>
+  </si>
+  <si>
+    <t>1.5 x 8ft</t>
+  </si>
+  <si>
+    <t>Foam Board 2 in thickness</t>
   </si>
 </sst>
 </file>
@@ -855,7 +858,7 @@
       </c>
       <c r="B1" s="4">
         <f>SUM('Per Assembly Cost --&gt;'!B:B)</f>
-        <v>375.10741778975739</v>
+        <v>384.10741778975739</v>
       </c>
     </row>
   </sheetData>
@@ -907,7 +910,7 @@
       </c>
       <c r="B3" s="1">
         <f>SUM('Structures BOM'!D:D)</f>
-        <v>163.273</v>
+        <v>172.273</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1146,13 +1149,13 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="1">
-        <v>1</v>
       </c>
       <c r="D3" s="1">
         <f>55.6/2*0.75</f>
@@ -1582,7 +1585,7 @@
         <v>23</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D24" s="1">
         <f>6.98/2</f>
@@ -1597,22 +1600,22 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D25" s="1">
-        <v>26.98</v>
+        <v>35.979999999999997</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="I25" s="8"/>
     </row>
@@ -1766,7 +1769,7 @@
         <v>52</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M5" s="8"/>
     </row>
@@ -1868,7 +1871,7 @@
         <v>53</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
@@ -2025,6 +2028,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c440327c-db0c-40f7-973b-7bc2ae283ce2" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006F9431A864773547893222757859AEDB" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8d93b3794edbd64c1f12ce1859fb2ebb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c440327c-db0c-40f7-973b-7bc2ae283ce2" xmlns:ns4="3bf09d50-f695-4e18-a2ec-955b0ff6d5dc" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ab198344f7607dd971ab6c53863418c3" ns3:_="" ns4:_="">
     <xsd:import namespace="c440327c-db0c-40f7-973b-7bc2ae283ce2"/>
@@ -2249,38 +2269,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c440327c-db0c-40f7-973b-7bc2ae283ce2" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92C5615A-B0FE-40B8-955A-C3851BD0A604}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{140E0E22-42B5-4B4A-934D-04548B25B00B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="c440327c-db0c-40f7-973b-7bc2ae283ce2"/>
-    <ds:schemaRef ds:uri="3bf09d50-f695-4e18-a2ec-955b0ff6d5dc"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2303,9 +2295,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{140E0E22-42B5-4B4A-934D-04548B25B00B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92C5615A-B0FE-40B8-955A-C3851BD0A604}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="c440327c-db0c-40f7-973b-7bc2ae283ce2"/>
+    <ds:schemaRef ds:uri="3bf09d50-f695-4e18-a2ec-955b0ff6d5dc"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/CostBreakdown.xlsx
+++ b/CostBreakdown.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jpreisle\Documents\GitHub\451-DBF-Team01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CB74598-2BA3-4CF1-BEE9-BC6238BC5F7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEFE5DDB-3C99-450D-B6EC-6D500444FE67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="831" activeTab="5" xr2:uid="{C684E4FE-65D8-41BB-8319-3046AEA9131B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="831" activeTab="2" xr2:uid="{C684E4FE-65D8-41BB-8319-3046AEA9131B}"/>
   </bookViews>
   <sheets>
     <sheet name="Aircraft Cost Grand Total" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="103">
   <si>
     <t>M4 30mm bolt</t>
   </si>
@@ -220,33 +220,18 @@
     <t>https://us.store.bambulab.com/products/pla-basic-filament?id=42844629008520</t>
   </si>
   <si>
-    <t>Servo Mount PLA</t>
-  </si>
-  <si>
-    <t>Motor Cover Print PLA</t>
-  </si>
-  <si>
-    <t>Wing Dihedral Print PLA</t>
-  </si>
-  <si>
     <t>Tail Mount Print ABS</t>
   </si>
   <si>
     <t>https://us.store.bambulab.com/products/abs-filament</t>
   </si>
   <si>
-    <t>Airspeed Sensor Print PLA</t>
-  </si>
-  <si>
     <t>https://www.mcmaster.com/12205T76/</t>
   </si>
   <si>
     <t>12 ft</t>
   </si>
   <si>
-    <t>Dowels</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gorilla Wood Glue </t>
   </si>
   <si>
@@ -295,12 +280,6 @@
     <t>adhesive velcro singe sided</t>
   </si>
   <si>
-    <t>5 ft</t>
-  </si>
-  <si>
-    <t>https://www.mcmaster.com/94985K27/</t>
-  </si>
-  <si>
     <t>Duct tape</t>
   </si>
   <si>
@@ -334,18 +313,12 @@
     <t>11x7E Prop</t>
   </si>
   <si>
-    <t>m2 servo screws</t>
-  </si>
-  <si>
     <t>39 in</t>
   </si>
   <si>
     <t>https://www.amazon.com/uxcell-Stainless-Crafts-Helicopter-Airplane/dp/B0F9FLP8ZX/ref=sr_1_1_sspa?crid=34B8IE94O70HA&amp;dib=eyJ2IjoiMSJ9.cU7lrr51XJ6qmYJOtUckRNTVaDGZtMfpKsb4a1nnoWj_3mOwmRlwX9K110lpATxnRlj8VJAXT0BzvVN4j66zfWec5g2koLZJikNByrNtigidG0j0aomu5dc6oTT4FSrP6QrbriTjrcd4Sniqtx8jaakzQk0pkfL_5sQx-lfLcv_kOWs8mObVOVKBTt2oJkXN8LWZhnXeWwgc5mSLuX2crPxBPMxIA-lzOSfG6GJ7Wp0.ZYBiy1ApnXie17T9Ypp93rQ6LX8hMn0YDRb8uOdDDxM&amp;dib_tag=se&amp;keywords=2mm+control+rod+steel&amp;qid=1792720495&amp;sprefix=2mm+control+rod+ste%2Caps%2C263&amp;sr=8-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1</t>
   </si>
   <si>
-    <t>https://www.mcmaster.com/92095A457/</t>
-  </si>
-  <si>
     <t>1/2 package</t>
   </si>
   <si>
@@ -359,6 +332,27 @@
   </si>
   <si>
     <t>Foam Board 2 in thickness</t>
+  </si>
+  <si>
+    <t>1.5 ft</t>
+  </si>
+  <si>
+    <t>https://www.homedepot.com/p/VELCRO-5-ft-x-3-4-in-Sticky-Back-Tape-90086/202261917</t>
+  </si>
+  <si>
+    <t>Shared</t>
+  </si>
+  <si>
+    <t>Airspeed Sensor Print ABS</t>
+  </si>
+  <si>
+    <t>Wing Dihedral Print ABS</t>
+  </si>
+  <si>
+    <t>Motor Cover Print PETG</t>
+  </si>
+  <si>
+    <t>Servo Mount ABS</t>
   </si>
 </sst>
 </file>
@@ -858,7 +852,7 @@
       </c>
       <c r="B1" s="4">
         <f>SUM('Per Assembly Cost --&gt;'!B:B)</f>
-        <v>384.10741778975739</v>
+        <v>379.50366666666662</v>
       </c>
     </row>
   </sheetData>
@@ -901,7 +895,7 @@
       </c>
       <c r="B2" s="5">
         <f>SUM('Avionics BOM'!D:D)</f>
-        <v>14.695417789757411</v>
+        <v>15.12</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -910,7 +904,7 @@
       </c>
       <c r="B3" s="1">
         <f>SUM('Structures BOM'!D:D)</f>
-        <v>172.273</v>
+        <v>165.94299999999998</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -919,7 +913,7 @@
       </c>
       <c r="B4" s="1">
         <f>SUM('Mechanisms BOM'!D:D)</f>
-        <v>55.918999999999997</v>
+        <v>57.220666666666666</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -941,7 +935,7 @@
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.28515625" customWidth="1"/>
@@ -952,7 +946,7 @@
     <col min="6" max="6" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -972,7 +966,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>41</v>
       </c>
@@ -991,8 +985,9 @@
       <c r="F2" s="3" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>43</v>
       </c>
@@ -1011,8 +1006,9 @@
       <c r="F3" s="3" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -1032,8 +1028,9 @@
       <c r="F4" s="3" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>32</v>
       </c>
@@ -1044,8 +1041,7 @@
         <v>20</v>
       </c>
       <c r="D5" s="5">
-        <f>20/7.42</f>
-        <v>2.6954177897574123</v>
+        <v>2.4</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>52</v>
@@ -1053,10 +1049,11 @@
       <c r="F5" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>34</v>
@@ -1065,7 +1062,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="1">
-        <v>0.28000000000000003</v>
+        <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>34</v>
@@ -1073,9 +1070,10 @@
       <c r="F6" s="3" t="s">
         <v>57</v>
       </c>
+      <c r="G6" s="1"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E1:E1048576">
+  <conditionalFormatting sqref="E1:E1048576 G2:G6">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"Y"</formula>
     </cfRule>
@@ -1096,7 +1094,7 @@
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.5703125" bestFit="1" customWidth="1"/>
@@ -1129,13 +1127,13 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D2" s="1">
         <v>8.08</v>
@@ -1144,18 +1142,19 @@
         <v>52</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>91</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="D3" s="1">
         <f>55.6/2*0.75</f>
@@ -1167,6 +1166,7 @@
       <c r="F3" s="3" t="s">
         <v>22</v>
       </c>
+      <c r="G3" s="1"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -1187,6 +1187,7 @@
       <c r="F4" s="3" t="s">
         <v>20</v>
       </c>
+      <c r="G4" s="1"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -1207,6 +1208,7 @@
       <c r="F5" s="3" t="s">
         <v>37</v>
       </c>
+      <c r="G5" s="1"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -1227,6 +1229,7 @@
       <c r="F6" s="3" t="s">
         <v>21</v>
       </c>
+      <c r="G6" s="1"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -1247,6 +1250,7 @@
       <c r="F7" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="G7" s="1"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -1267,6 +1271,7 @@
       <c r="F8" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -1287,6 +1292,7 @@
       <c r="F9" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="G9" s="1"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -1307,6 +1313,7 @@
       <c r="F10" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="G10" s="1"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -1327,16 +1334,17 @@
       <c r="F11" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="G11" s="1"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D12" s="5">
         <f>4.98/8*6</f>
@@ -1346,18 +1354,19 @@
         <v>52</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>69</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="G12" s="1"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D13" s="5">
         <f>9.98*0.6</f>
@@ -1367,13 +1376,14 @@
         <v>52</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>71</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="G13" s="1"/>
       <c r="N13" s="8"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>23</v>
@@ -1389,8 +1399,9 @@
         <v>53</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>73</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="G14" s="1"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
@@ -1400,7 +1411,7 @@
         <v>23</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D15" s="1">
         <v>4.07</v>
@@ -1411,10 +1422,11 @@
       <c r="F15" s="3" t="s">
         <v>49</v>
       </c>
+      <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>34</v>
@@ -1423,18 +1435,19 @@
         <v>1</v>
       </c>
       <c r="D16" s="1">
-        <v>1.0900000000000001</v>
+        <v>1</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>62</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="G16" s="1"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>34</v>
@@ -1443,7 +1456,7 @@
         <v>1</v>
       </c>
       <c r="D17" s="1">
-        <v>0.06</v>
+        <v>0.5</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>34</v>
@@ -1451,10 +1464,11 @@
       <c r="F17" s="3" t="s">
         <v>57</v>
       </c>
+      <c r="G17" s="1"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>34</v>
@@ -1463,119 +1477,126 @@
         <v>1</v>
       </c>
       <c r="D18" s="1">
-        <v>0.67</v>
+        <v>2</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>78</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="G18" s="1"/>
       <c r="N18" s="8"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C19" s="1">
-        <v>4</v>
+        <v>23</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="D19" s="1">
-        <v>0.05</v>
+        <v>0.51</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>62</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="G19" s="1"/>
+      <c r="N19" s="8"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="D20" s="1">
-        <v>0.51</v>
+        <v>2.48</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>79</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="G20" s="1"/>
       <c r="N20" s="8"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D21" s="1">
-        <v>7.76</v>
+        <v>0.39</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>84</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="G21" s="1"/>
       <c r="N21" s="8"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>86</v>
+      <c r="C22" s="1">
+        <v>1</v>
       </c>
       <c r="D22" s="1">
-        <v>0.39</v>
+        <v>0.03</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>52</v>
+        <v>98</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>87</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="G22" s="1"/>
       <c r="N22" s="8"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="1">
-        <v>100</v>
+      <c r="C23" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="D23" s="1">
-        <v>2.71</v>
+        <f>6.98/2</f>
+        <v>3.49</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="N23" s="8"/>
+        <v>86</v>
+      </c>
+      <c r="G23" s="1"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
@@ -1585,42 +1606,22 @@
         <v>23</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="D24" s="1">
-        <f>6.98/2</f>
-        <v>3.49</v>
+        <v>35.979999999999997</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>101</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D25" s="1">
-        <v>35.979999999999997</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="I25" s="8"/>
+      <c r="G24" s="1"/>
+      <c r="I24" s="8"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E1:E1048576">
+  <conditionalFormatting sqref="E1:E1048576 G2:G24">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Y"</formula>
     </cfRule>
@@ -1640,15 +1641,15 @@
     <hyperlink ref="F7" r:id="rId12" xr:uid="{3C1E28BD-D3E4-46AC-A0D8-E327EE566BE4}"/>
     <hyperlink ref="F9" r:id="rId13" xr:uid="{751BAEB2-26DC-4CAF-8D96-A38FD9446E87}"/>
     <hyperlink ref="F11" r:id="rId14" xr:uid="{9B3802E2-0DAA-4495-8E7B-C8A9F6A2FFA8}"/>
-    <hyperlink ref="F19" r:id="rId15" xr:uid="{8B7798E1-B9EF-4C27-8F45-57F8754CF6C6}"/>
-    <hyperlink ref="F12" r:id="rId16" xr:uid="{DAC881B0-F10F-4F69-8986-0AAA523A24EF}"/>
-    <hyperlink ref="F21" r:id="rId17" xr:uid="{B1936492-E69E-4FC0-9317-A51FD4D180C9}"/>
-    <hyperlink ref="F20" r:id="rId18" display="https://www.uline.com/Product/Detail/S-24954/3M-Double-Sided-Tape/3M-GPT-020-Double-Coated-Tape-1-2-x-55-yds?pricode=WB2129&amp;gadtype=pla&amp;id=S-24954&amp;ad_group_id=145971513970&amp;gad_source=1&amp;gad_campaignid=11612151501&amp;gbraid=0AAAAAD_uetMWPvmgHv3q_pW1Ap2XPjNcU&amp;gclid=CjwKCAjwxeHWBhBPEiwAiqtQ-fXMrRlgI_ldfpzj6iy0tx9E9ZY5jWXLAkurdtsnGW43uC5BHwLfohoCeCEQAvD_BwE" xr:uid="{5269E7F4-3C12-41E9-B94C-7D7110BCCB5B}"/>
-    <hyperlink ref="F13" r:id="rId19" xr:uid="{02A4D3AB-EDC0-4B65-841E-3298AA137928}"/>
-    <hyperlink ref="F22" r:id="rId20" xr:uid="{14143E63-1487-40FC-AEB3-356D1822FE75}"/>
-    <hyperlink ref="F23" r:id="rId21" xr:uid="{B7AFD8AB-FA10-4D01-851E-CFAF953BAB8E}"/>
-    <hyperlink ref="F25" r:id="rId22" xr:uid="{220600F5-F3D8-4713-9FCF-D0034B1ED51A}"/>
-    <hyperlink ref="F24" r:id="rId23" xr:uid="{25340820-4495-4BA4-8066-28EF3BFF3F70}"/>
+    <hyperlink ref="F12" r:id="rId15" xr:uid="{DAC881B0-F10F-4F69-8986-0AAA523A24EF}"/>
+    <hyperlink ref="F20" r:id="rId16" xr:uid="{B1936492-E69E-4FC0-9317-A51FD4D180C9}"/>
+    <hyperlink ref="F19" r:id="rId17" display="https://www.uline.com/Product/Detail/S-24954/3M-Double-Sided-Tape/3M-GPT-020-Double-Coated-Tape-1-2-x-55-yds?pricode=WB2129&amp;gadtype=pla&amp;id=S-24954&amp;ad_group_id=145971513970&amp;gad_source=1&amp;gad_campaignid=11612151501&amp;gbraid=0AAAAAD_uetMWPvmgHv3q_pW1Ap2XPjNcU&amp;gclid=CjwKCAjwxeHWBhBPEiwAiqtQ-fXMrRlgI_ldfpzj6iy0tx9E9ZY5jWXLAkurdtsnGW43uC5BHwLfohoCeCEQAvD_BwE" xr:uid="{5269E7F4-3C12-41E9-B94C-7D7110BCCB5B}"/>
+    <hyperlink ref="F13" r:id="rId18" xr:uid="{02A4D3AB-EDC0-4B65-841E-3298AA137928}"/>
+    <hyperlink ref="F21" r:id="rId19" xr:uid="{14143E63-1487-40FC-AEB3-356D1822FE75}"/>
+    <hyperlink ref="F22" r:id="rId20" xr:uid="{B7AFD8AB-FA10-4D01-851E-CFAF953BAB8E}"/>
+    <hyperlink ref="F24" r:id="rId21" xr:uid="{220600F5-F3D8-4713-9FCF-D0034B1ED51A}"/>
+    <hyperlink ref="F23" r:id="rId22" xr:uid="{25340820-4495-4BA4-8066-28EF3BFF3F70}"/>
+    <hyperlink ref="F2" r:id="rId23" xr:uid="{281C40FF-70EC-493D-84E2-2E1AFD09ECE0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId24"/>
@@ -1713,7 +1714,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>58</v>
+        <v>102</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>34</v>
@@ -1722,7 +1723,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="1">
-        <v>0.11</v>
+        <v>0.5</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>34</v>
@@ -1769,7 +1770,7 @@
         <v>52</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="M5" s="8"/>
     </row>
@@ -1804,8 +1805,8 @@
         <v>2</v>
       </c>
       <c r="D7" s="5">
-        <f>11.99/2</f>
-        <v>5.9950000000000001</v>
+        <f>16.99/3*2</f>
+        <v>11.326666666666666</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>52</v>
@@ -1851,27 +1852,7 @@
         <v>52</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>96</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="1">
-        <v>25</v>
-      </c>
-      <c r="D10" s="1">
-        <v>4.42</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>99</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
@@ -1886,9 +1867,9 @@
   <hyperlinks>
     <hyperlink ref="F7" r:id="rId1" xr:uid="{53C4CC5E-18BB-493C-B4BF-A5DBA279DD54}"/>
     <hyperlink ref="F6" r:id="rId2" xr:uid="{0004C175-5738-4B8F-BD83-32A5A30FB28E}"/>
-    <hyperlink ref="F4" r:id="rId3" xr:uid="{0E92F0AD-782A-4CF6-8DF2-62BFB580A776}"/>
-    <hyperlink ref="F3" r:id="rId4" xr:uid="{7B1E3156-A427-4EE6-BDAE-640964CFC534}"/>
-    <hyperlink ref="F9" r:id="rId5" xr:uid="{4D5B5F44-6C1C-49C0-8972-E0BE3BA5E7E1}"/>
+    <hyperlink ref="F3" r:id="rId3" xr:uid="{7B1E3156-A427-4EE6-BDAE-640964CFC534}"/>
+    <hyperlink ref="F9" r:id="rId4" xr:uid="{4D5B5F44-6C1C-49C0-8972-E0BE3BA5E7E1}"/>
+    <hyperlink ref="F4" r:id="rId5" xr:uid="{0E92F0AD-782A-4CF6-8DF2-62BFB580A776}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1931,7 +1912,7 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>23</v>
@@ -1946,13 +1927,14 @@
         <v>52</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>94</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="G2" s="1"/>
       <c r="M2" s="8"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>23</v>
@@ -1967,8 +1949,9 @@
         <v>52</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>77</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="G3" s="1"/>
       <c r="M3" s="8"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -1990,6 +1973,7 @@
       <c r="F4" s="3" t="s">
         <v>29</v>
       </c>
+      <c r="G4" s="1"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -2010,9 +1994,10 @@
       <c r="F5" s="3" t="s">
         <v>30</v>
       </c>
+      <c r="G5" s="1"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E1:E1048576">
+  <conditionalFormatting sqref="E1:E1048576 G2:G5">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"Y"</formula>
     </cfRule>
